--- a/[서버]_FAP_정기점검/templates/server_report_form.xlsx
+++ b/[서버]_FAP_정기점검/templates/server_report_form.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgjan\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgjan\AppData\Roaming\MobaXterm\slash\mx86_64b\RemoteFiles\1313484_6_53\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B8A252-6C18-498D-B733-5052D9B5C8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B3857C-BDF9-438C-9842-5240468F66A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29790" yWindow="-120" windowWidth="27930" windowHeight="16440" xr2:uid="{F40717F4-5740-4B20-A9D7-5EC8DA815EF1}"/>
+    <workbookView xWindow="1080" yWindow="-108" windowWidth="22068" windowHeight="13176" xr2:uid="{F40717F4-5740-4B20-A9D7-5EC8DA815EF1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="155">
   <si>
     <t>자동화 서버 시스템 통상점검 일지</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -683,6 +683,10 @@
       </rPr>
       <t>free –h</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관리자 그룹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -918,158 +922,158 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1408,2287 +1412,2367 @@
   <dimension ref="A2:M203"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="20.09765625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="10.09765625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.296875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="13.69921875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="12.296875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="14.8984375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="17.09765625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="8.796875" style="3"/>
-    <col min="9" max="9" width="5.19921875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.19921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.796875" style="3"/>
-    <col min="13" max="13" width="4.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="3"/>
+    <col min="1" max="1" width="20.09765625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.09765625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.296875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.69921875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.296875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.8984375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.09765625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.796875" style="2"/>
+    <col min="9" max="9" width="5.19921875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.796875" style="2"/>
+    <col min="13" max="13" width="4.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.796875" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="30" t="s">
+      <c r="B3" s="25"/>
+      <c r="C3" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
     </row>
     <row r="4" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="5" t="s">
+      <c r="F4" s="3"/>
+      <c r="G4" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="4" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="5" t="s">
+      <c r="F5" s="3"/>
+      <c r="G5" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="30" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
     </row>
     <row r="7" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="2" t="s">
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="36"/>
-      <c r="B8" s="4">
+      <c r="A8" s="43"/>
+      <c r="B8" s="3">
         <v>1</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="4" t="s">
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="36"/>
-      <c r="B9" s="4">
+      <c r="A9" s="43"/>
+      <c r="B9" s="3">
         <v>2</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="4" t="s">
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="36"/>
-      <c r="B10" s="4">
+      <c r="A10" s="43"/>
+      <c r="B10" s="3">
         <v>3</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="4" t="s">
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="36"/>
-      <c r="B11" s="4">
+      <c r="A11" s="43"/>
+      <c r="B11" s="3">
         <v>4</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="4" t="s">
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="36"/>
-      <c r="B12" s="4">
+      <c r="A12" s="43"/>
+      <c r="B12" s="3">
         <v>5</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="4" t="s">
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="36"/>
-      <c r="B13" s="4">
+      <c r="A13" s="43"/>
+      <c r="B13" s="3">
         <v>6</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="4" t="s">
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="36"/>
-      <c r="B14" s="4">
+      <c r="A14" s="43"/>
+      <c r="B14" s="3">
         <v>7</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="4" t="s">
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="36"/>
-      <c r="B15" s="4">
+      <c r="A15" s="43"/>
+      <c r="B15" s="3">
         <v>8</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="4" t="s">
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="37"/>
-      <c r="B16" s="4">
+      <c r="A16" s="44"/>
+      <c r="B16" s="3">
         <v>9</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="4" t="s">
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
     </row>
     <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="31"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
+      <c r="A18" s="25"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
     </row>
     <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="31"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
     </row>
     <row r="22" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="22" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="31"/>
-      <c r="D23" s="2" t="s">
+      <c r="C23" s="25"/>
+      <c r="D23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="31" t="s">
+      <c r="E23" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="31"/>
-      <c r="G23" s="2" t="s">
+      <c r="F23" s="25"/>
+      <c r="G23" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="6" t="s">
+      <c r="C24" s="48"/>
+      <c r="D24" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="28" t="s">
+      <c r="E24" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="F24" s="28"/>
-      <c r="G24" s="4" t="s">
+      <c r="F24" s="48"/>
+      <c r="G24" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="6" t="s">
+      <c r="C25" s="48"/>
+      <c r="D25" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="28" t="s">
+      <c r="E25" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="28"/>
-      <c r="G25" s="4" t="s">
+      <c r="F25" s="48"/>
+      <c r="G25" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
     </row>
     <row r="28" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="22" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B29" s="31" t="s">
+      <c r="B29" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31" t="s">
+      <c r="C29" s="25"/>
+      <c r="D29" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31" t="s">
+      <c r="E29" s="25"/>
+      <c r="F29" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="G29" s="31"/>
+      <c r="G29" s="25"/>
     </row>
     <row r="30" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="48"/>
     </row>
     <row r="31" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
     </row>
     <row r="32" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
     </row>
     <row r="33" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
     </row>
     <row r="34" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
     </row>
     <row r="35" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
     </row>
     <row r="36" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
     </row>
     <row r="41" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="51" t="s">
+      <c r="A41" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B41" s="51"/>
-      <c r="C41" s="51"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
     </row>
     <row r="42" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="50" t="s">
+      <c r="A42" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="B42" s="50"/>
-      <c r="C42" s="50"/>
-      <c r="D42" s="50"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
+      <c r="B42" s="39"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
     </row>
     <row r="43" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="22" t="s">
+      <c r="A43" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
     </row>
     <row r="44" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="22" t="s">
+      <c r="A44" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
     </row>
     <row r="45" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="22" t="s">
+      <c r="A45" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="22"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
     </row>
     <row r="46" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="22" t="s">
+      <c r="A46" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
     </row>
     <row r="47" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="29" t="s">
+      <c r="A47" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="9" t="s">
+      <c r="B47" s="50"/>
+      <c r="C47" s="50"/>
+      <c r="D47" s="50"/>
+      <c r="E47" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
     </row>
     <row r="48" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="28"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
+      <c r="A48" s="48"/>
+      <c r="B48" s="48"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="48"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
     </row>
     <row r="49" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="10"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
+      <c r="A49" s="9"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
     </row>
     <row r="50" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="22" t="s">
+      <c r="A50" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="B50" s="22"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
+      <c r="B50" s="37"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
     </row>
     <row r="51" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="29" t="s">
+      <c r="A51" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="9" t="s">
+      <c r="B51" s="50"/>
+      <c r="C51" s="50"/>
+      <c r="D51" s="50"/>
+      <c r="E51" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
     </row>
     <row r="52" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="28"/>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
+      <c r="A52" s="48"/>
+      <c r="B52" s="48"/>
+      <c r="C52" s="48"/>
+      <c r="D52" s="48"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
     </row>
     <row r="53" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="10"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
+      <c r="A53" s="9"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7"/>
     </row>
     <row r="54" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="50" t="s">
+      <c r="A54" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="B54" s="50"/>
-      <c r="C54" s="50"/>
-      <c r="D54" s="50"/>
-      <c r="E54" s="50"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
+      <c r="B54" s="39"/>
+      <c r="C54" s="39"/>
+      <c r="D54" s="39"/>
+      <c r="E54" s="39"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
     </row>
     <row r="55" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="22" t="s">
+      <c r="A55" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="B55" s="22"/>
-      <c r="C55" s="22"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
+      <c r="B55" s="37"/>
+      <c r="C55" s="37"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="37"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
     </row>
     <row r="56" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="22" t="s">
+      <c r="A56" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="B56" s="22"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
+      <c r="B56" s="37"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
     </row>
     <row r="57" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="22" t="s">
+      <c r="A57" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="B57" s="22"/>
-      <c r="C57" s="22"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
+      <c r="B57" s="37"/>
+      <c r="C57" s="37"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
     </row>
     <row r="58" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="22" t="s">
+      <c r="A58" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="B58" s="22"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
+      <c r="B58" s="37"/>
+      <c r="C58" s="37"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="37"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
     </row>
     <row r="59" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="9" t="s">
+      <c r="A59" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D59" s="9" t="s">
+      <c r="D59" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E59" s="9" t="s">
+      <c r="E59" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
     </row>
     <row r="60" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
     </row>
     <row r="61" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
     </row>
     <row r="62" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
     </row>
     <row r="63" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="10"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
+      <c r="A63" s="9"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
     </row>
     <row r="64" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="22" t="s">
+      <c r="A64" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="B64" s="22"/>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="8"/>
+      <c r="B64" s="37"/>
+      <c r="C64" s="37"/>
+      <c r="D64" s="37"/>
+      <c r="E64" s="37"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="7"/>
     </row>
     <row r="65" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="9" t="s">
+      <c r="A65" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C65" s="9" t="s">
+      <c r="C65" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D65" s="9" t="s">
+      <c r="D65" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E65" s="9" t="s">
+      <c r="E65" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
     </row>
     <row r="66" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="7"/>
     </row>
     <row r="67" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="8"/>
-      <c r="G67" s="8"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="10"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="7"/>
     </row>
     <row r="68" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
     </row>
     <row r="69" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="10"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
+      <c r="A69" s="9"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
     </row>
     <row r="70" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="50" t="s">
+      <c r="A70" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="B70" s="50"/>
-      <c r="C70" s="50"/>
-      <c r="D70" s="50"/>
-      <c r="E70" s="50"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
+      <c r="B70" s="39"/>
+      <c r="C70" s="39"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
     </row>
     <row r="71" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="22" t="s">
+      <c r="A71" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="B71" s="22"/>
-      <c r="C71" s="22"/>
-      <c r="D71" s="22"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
+      <c r="B71" s="37"/>
+      <c r="C71" s="37"/>
+      <c r="D71" s="37"/>
+      <c r="E71" s="37"/>
+      <c r="F71" s="7"/>
+      <c r="G71" s="7"/>
     </row>
     <row r="72" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="22" t="s">
+      <c r="A72" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="B72" s="22"/>
-      <c r="C72" s="22"/>
-      <c r="D72" s="22"/>
-      <c r="E72" s="22"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
+      <c r="B72" s="37"/>
+      <c r="C72" s="37"/>
+      <c r="D72" s="37"/>
+      <c r="E72" s="37"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="7"/>
     </row>
     <row r="73" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="22" t="s">
+      <c r="A73" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="B73" s="22"/>
-      <c r="C73" s="22"/>
-      <c r="D73" s="22"/>
-      <c r="E73" s="22"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
+      <c r="B73" s="37"/>
+      <c r="C73" s="37"/>
+      <c r="D73" s="37"/>
+      <c r="E73" s="37"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="7"/>
     </row>
     <row r="74" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="22" t="s">
+      <c r="A74" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="B74" s="22"/>
-      <c r="C74" s="22"/>
-      <c r="D74" s="22"/>
-      <c r="E74" s="22"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
+      <c r="B74" s="37"/>
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="37"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
     </row>
     <row r="75" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="9" t="s">
+      <c r="A75" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B75" s="29" t="s">
+      <c r="B75" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="C75" s="29"/>
-      <c r="D75" s="9" t="s">
+      <c r="C75" s="50"/>
+      <c r="D75" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="7"/>
     </row>
     <row r="76" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B76" s="28"/>
-      <c r="C76" s="28"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
+      <c r="G76" s="7"/>
     </row>
     <row r="77" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="10"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
+      <c r="A77" s="9"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
     </row>
     <row r="78" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="22" t="s">
+      <c r="A78" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="B78" s="22"/>
-      <c r="C78" s="22"/>
-      <c r="D78" s="22"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
+      <c r="B78" s="37"/>
+      <c r="C78" s="37"/>
+      <c r="D78" s="37"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="7"/>
+      <c r="G78" s="7"/>
     </row>
     <row r="79" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="9" t="s">
+      <c r="A79" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B79" s="29" t="s">
+      <c r="B79" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="C79" s="29"/>
-      <c r="D79" s="9" t="s">
+      <c r="C79" s="50"/>
+      <c r="D79" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="7"/>
     </row>
     <row r="80" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B80" s="28"/>
-      <c r="C80" s="28"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
+      <c r="B80" s="48"/>
+      <c r="C80" s="48"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7"/>
     </row>
     <row r="81" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="12"/>
-      <c r="B81" s="12"/>
-      <c r="C81" s="12"/>
-      <c r="D81" s="12"/>
-      <c r="E81" s="12"/>
-      <c r="F81" s="12"/>
-      <c r="G81" s="12"/>
+      <c r="A81" s="11"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
     </row>
     <row r="82" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="51" t="s">
+      <c r="A82" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="B82" s="51"/>
-      <c r="C82" s="51"/>
-      <c r="D82" s="51"/>
-      <c r="E82" s="51"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="12"/>
-    </row>
-    <row r="83" spans="1:7" s="14" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="13" t="s">
+      <c r="B82" s="23"/>
+      <c r="C82" s="23"/>
+      <c r="D82" s="23"/>
+      <c r="E82" s="23"/>
+      <c r="F82" s="11"/>
+      <c r="G82" s="11"/>
+    </row>
+    <row r="83" spans="1:7" s="13" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B83" s="27" t="s">
+      <c r="B83" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="C83" s="27"/>
-      <c r="D83" s="27" t="s">
+      <c r="C83" s="38"/>
+      <c r="D83" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="E83" s="27"/>
-      <c r="F83" s="27" t="s">
+      <c r="E83" s="38"/>
+      <c r="F83" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="G83" s="27"/>
+      <c r="G83" s="38"/>
     </row>
     <row r="84" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="15" t="s">
+      <c r="A84" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="B84" s="28"/>
-      <c r="C84" s="28"/>
-      <c r="D84" s="28"/>
-      <c r="E84" s="28"/>
-      <c r="F84" s="28"/>
-      <c r="G84" s="28"/>
+      <c r="B84" s="48"/>
+      <c r="C84" s="48"/>
+      <c r="D84" s="48"/>
+      <c r="E84" s="48"/>
+      <c r="F84" s="48"/>
+      <c r="G84" s="48"/>
     </row>
     <row r="85" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="15" t="s">
+      <c r="A85" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B85" s="28"/>
-      <c r="C85" s="28"/>
-      <c r="D85" s="28"/>
-      <c r="E85" s="28"/>
-      <c r="F85" s="28"/>
-      <c r="G85" s="28"/>
+      <c r="B85" s="48"/>
+      <c r="C85" s="48"/>
+      <c r="D85" s="48"/>
+      <c r="E85" s="48"/>
+      <c r="F85" s="48"/>
+      <c r="G85" s="48"/>
     </row>
     <row r="86" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="15" t="s">
+      <c r="A86" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="B86" s="28"/>
-      <c r="C86" s="28"/>
-      <c r="D86" s="28"/>
-      <c r="E86" s="28"/>
-      <c r="F86" s="28"/>
-      <c r="G86" s="28"/>
+      <c r="B86" s="48"/>
+      <c r="C86" s="48"/>
+      <c r="D86" s="48"/>
+      <c r="E86" s="48"/>
+      <c r="F86" s="48"/>
+      <c r="G86" s="48"/>
     </row>
     <row r="87" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="12"/>
-      <c r="B87" s="12"/>
-      <c r="C87" s="12"/>
-      <c r="D87" s="12"/>
-      <c r="E87" s="12"/>
-      <c r="F87" s="12"/>
-      <c r="G87" s="12"/>
+      <c r="A87" s="11"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="11"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
+      <c r="F87" s="11"/>
+      <c r="G87" s="11"/>
     </row>
     <row r="88" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="12"/>
-      <c r="B88" s="12"/>
-      <c r="C88" s="12"/>
-      <c r="D88" s="12"/>
-      <c r="E88" s="12"/>
-      <c r="F88" s="12"/>
-      <c r="G88" s="12"/>
+      <c r="A88" s="11"/>
+      <c r="B88" s="11"/>
+      <c r="C88" s="11"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
+      <c r="F88" s="11"/>
+      <c r="G88" s="11"/>
     </row>
     <row r="89" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="51" t="s">
+      <c r="A89" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B89" s="51"/>
-      <c r="C89" s="51"/>
-      <c r="D89" s="51"/>
-      <c r="E89" s="51"/>
-      <c r="F89" s="12"/>
-      <c r="G89" s="12"/>
+      <c r="B89" s="23"/>
+      <c r="C89" s="23"/>
+      <c r="D89" s="23"/>
+      <c r="E89" s="23"/>
+      <c r="F89" s="11"/>
+      <c r="G89" s="11"/>
     </row>
     <row r="90" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="50" t="s">
+      <c r="A90" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="B90" s="50"/>
-      <c r="C90" s="50"/>
-      <c r="D90" s="50"/>
-      <c r="E90" s="50"/>
-      <c r="F90" s="12"/>
-      <c r="G90" s="12"/>
+      <c r="B90" s="39"/>
+      <c r="C90" s="39"/>
+      <c r="D90" s="39"/>
+      <c r="E90" s="39"/>
+      <c r="F90" s="11"/>
+      <c r="G90" s="11"/>
     </row>
     <row r="91" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="22" t="s">
+      <c r="A91" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="B91" s="22"/>
-      <c r="C91" s="22"/>
-      <c r="D91" s="22"/>
-      <c r="E91" s="22"/>
-      <c r="F91" s="12"/>
-      <c r="G91" s="12"/>
-    </row>
-    <row r="92" spans="1:7" s="14" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="13" t="s">
+      <c r="B91" s="37"/>
+      <c r="C91" s="37"/>
+      <c r="D91" s="37"/>
+      <c r="E91" s="37"/>
+      <c r="F91" s="11"/>
+      <c r="G91" s="11"/>
+    </row>
+    <row r="92" spans="1:7" s="13" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B92" s="27" t="s">
+      <c r="B92" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="C92" s="27"/>
-      <c r="D92" s="27"/>
-      <c r="E92" s="13" t="s">
+      <c r="C92" s="38"/>
+      <c r="D92" s="38"/>
+      <c r="E92" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F92" s="27" t="s">
+      <c r="F92" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="G92" s="27"/>
+      <c r="G92" s="38"/>
     </row>
     <row r="93" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="6">
+      <c r="A93" s="5">
         <v>1</v>
       </c>
-      <c r="B93" s="41" t="s">
+      <c r="B93" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="C93" s="42"/>
-      <c r="D93" s="43"/>
-      <c r="E93" s="6"/>
-      <c r="F93" s="41"/>
-      <c r="G93" s="43"/>
+      <c r="C93" s="35"/>
+      <c r="D93" s="36"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="34"/>
+      <c r="G93" s="36"/>
     </row>
     <row r="94" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="6">
+      <c r="A94" s="5">
         <v>2</v>
       </c>
-      <c r="B94" s="41" t="s">
+      <c r="B94" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="C94" s="42"/>
-      <c r="D94" s="43"/>
-      <c r="E94" s="6"/>
-      <c r="F94" s="41"/>
-      <c r="G94" s="43"/>
+      <c r="C94" s="35"/>
+      <c r="D94" s="36"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="34"/>
+      <c r="G94" s="36"/>
     </row>
     <row r="95" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="6">
+      <c r="A95" s="5">
         <v>3</v>
       </c>
-      <c r="B95" s="41" t="s">
+      <c r="B95" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="C95" s="42"/>
-      <c r="D95" s="43"/>
-      <c r="E95" s="6"/>
-      <c r="F95" s="41"/>
-      <c r="G95" s="43"/>
+      <c r="C95" s="35"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="34"/>
+      <c r="G95" s="36"/>
     </row>
     <row r="96" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="6">
+      <c r="A96" s="5">
         <v>4</v>
       </c>
-      <c r="B96" s="41" t="s">
+      <c r="B96" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="C96" s="42"/>
-      <c r="D96" s="43"/>
-      <c r="E96" s="6"/>
-      <c r="F96" s="41"/>
-      <c r="G96" s="43"/>
+      <c r="C96" s="35"/>
+      <c r="D96" s="36"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="34"/>
+      <c r="G96" s="36"/>
     </row>
     <row r="97" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="6">
+      <c r="A97" s="5">
         <v>5</v>
       </c>
-      <c r="B97" s="41" t="s">
+      <c r="B97" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="C97" s="42"/>
-      <c r="D97" s="43"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="41"/>
-      <c r="G97" s="43"/>
+      <c r="C97" s="35"/>
+      <c r="D97" s="36"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="34"/>
+      <c r="G97" s="36"/>
     </row>
     <row r="98" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="6">
+      <c r="A98" s="5">
         <v>6</v>
       </c>
-      <c r="B98" s="41" t="s">
+      <c r="B98" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="C98" s="42"/>
-      <c r="D98" s="43"/>
-      <c r="E98" s="6"/>
-      <c r="F98" s="41"/>
-      <c r="G98" s="43"/>
+      <c r="C98" s="35"/>
+      <c r="D98" s="36"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="34"/>
+      <c r="G98" s="36"/>
     </row>
     <row r="99" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="6">
+      <c r="A99" s="5">
         <v>7</v>
       </c>
-      <c r="B99" s="41" t="s">
+      <c r="B99" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="C99" s="42"/>
-      <c r="D99" s="43"/>
-      <c r="E99" s="6"/>
-      <c r="F99" s="41"/>
-      <c r="G99" s="43"/>
+      <c r="C99" s="35"/>
+      <c r="D99" s="36"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="34"/>
+      <c r="G99" s="36"/>
     </row>
     <row r="100" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="12"/>
-      <c r="B100" s="12"/>
-      <c r="C100" s="12"/>
-      <c r="D100" s="12"/>
-      <c r="E100" s="12"/>
-      <c r="F100" s="12"/>
-      <c r="G100" s="12"/>
+      <c r="A100" s="11"/>
+      <c r="B100" s="11"/>
+      <c r="C100" s="11"/>
+      <c r="D100" s="11"/>
+      <c r="E100" s="11"/>
+      <c r="F100" s="11"/>
+      <c r="G100" s="11"/>
     </row>
     <row r="101" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="22" t="s">
+      <c r="A101" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="B101" s="22"/>
-      <c r="C101" s="22"/>
-      <c r="D101" s="22"/>
-      <c r="E101" s="22"/>
-      <c r="F101" s="12"/>
-      <c r="G101" s="12"/>
+      <c r="B101" s="37"/>
+      <c r="C101" s="37"/>
+      <c r="D101" s="37"/>
+      <c r="E101" s="37"/>
+      <c r="F101" s="11"/>
+      <c r="G101" s="11"/>
     </row>
     <row r="102" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="13" t="s">
+      <c r="A102" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B102" s="27" t="s">
+      <c r="B102" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="C102" s="27"/>
-      <c r="D102" s="27"/>
-      <c r="E102" s="13" t="s">
+      <c r="C102" s="38"/>
+      <c r="D102" s="38"/>
+      <c r="E102" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F102" s="27" t="s">
+      <c r="F102" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="G102" s="27"/>
+      <c r="G102" s="38"/>
     </row>
     <row r="103" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="6">
+      <c r="A103" s="5">
         <v>1</v>
       </c>
-      <c r="B103" s="41" t="s">
+      <c r="B103" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="C103" s="42"/>
-      <c r="D103" s="43"/>
-      <c r="E103" s="6"/>
-      <c r="F103" s="41"/>
-      <c r="G103" s="43"/>
+      <c r="C103" s="35"/>
+      <c r="D103" s="36"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="34"/>
+      <c r="G103" s="36"/>
     </row>
     <row r="104" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="6">
+      <c r="A104" s="5">
         <v>2</v>
       </c>
-      <c r="B104" s="41" t="s">
+      <c r="B104" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="C104" s="42"/>
-      <c r="D104" s="43"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="41"/>
-      <c r="G104" s="43"/>
+      <c r="C104" s="35"/>
+      <c r="D104" s="36"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="34"/>
+      <c r="G104" s="36"/>
     </row>
     <row r="105" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="6">
+      <c r="A105" s="5">
         <v>3</v>
       </c>
-      <c r="B105" s="41" t="s">
+      <c r="B105" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="C105" s="42"/>
-      <c r="D105" s="43"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="41"/>
-      <c r="G105" s="43"/>
+      <c r="C105" s="35"/>
+      <c r="D105" s="36"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="34"/>
+      <c r="G105" s="36"/>
     </row>
     <row r="106" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="6">
+      <c r="A106" s="5">
         <v>4</v>
       </c>
-      <c r="B106" s="41" t="s">
+      <c r="B106" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="C106" s="42"/>
-      <c r="D106" s="43"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="41"/>
-      <c r="G106" s="43"/>
+      <c r="C106" s="35"/>
+      <c r="D106" s="36"/>
+      <c r="E106" s="5"/>
+      <c r="F106" s="34"/>
+      <c r="G106" s="36"/>
     </row>
     <row r="107" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="6">
+      <c r="A107" s="5">
         <v>5</v>
       </c>
-      <c r="B107" s="41" t="s">
+      <c r="B107" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="C107" s="42"/>
-      <c r="D107" s="43"/>
-      <c r="E107" s="6"/>
-      <c r="F107" s="41"/>
-      <c r="G107" s="43"/>
+      <c r="C107" s="35"/>
+      <c r="D107" s="36"/>
+      <c r="E107" s="5"/>
+      <c r="F107" s="34"/>
+      <c r="G107" s="36"/>
     </row>
     <row r="108" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="6">
+      <c r="A108" s="5">
         <v>6</v>
       </c>
-      <c r="B108" s="41" t="s">
+      <c r="B108" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="C108" s="42"/>
-      <c r="D108" s="43"/>
-      <c r="E108" s="6"/>
-      <c r="F108" s="41"/>
-      <c r="G108" s="43"/>
+      <c r="C108" s="35"/>
+      <c r="D108" s="36"/>
+      <c r="E108" s="5"/>
+      <c r="F108" s="34"/>
+      <c r="G108" s="36"/>
     </row>
     <row r="109" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="6">
+      <c r="A109" s="5">
         <v>7</v>
       </c>
-      <c r="B109" s="41" t="s">
+      <c r="B109" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="C109" s="42"/>
-      <c r="D109" s="43"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="41"/>
-      <c r="G109" s="43"/>
+      <c r="C109" s="35"/>
+      <c r="D109" s="36"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="34"/>
+      <c r="G109" s="36"/>
     </row>
     <row r="110" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="16"/>
-      <c r="B110" s="16"/>
-      <c r="C110" s="16"/>
-      <c r="D110" s="16"/>
-      <c r="E110" s="16"/>
-      <c r="F110" s="16"/>
-      <c r="G110" s="16"/>
+      <c r="A110" s="15"/>
+      <c r="B110" s="15"/>
+      <c r="C110" s="15"/>
+      <c r="D110" s="15"/>
+      <c r="E110" s="15"/>
+      <c r="F110" s="15"/>
+      <c r="G110" s="15"/>
     </row>
     <row r="111" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="17"/>
-      <c r="B111" s="17"/>
-      <c r="C111" s="17"/>
-      <c r="D111" s="17"/>
-      <c r="E111" s="17"/>
-      <c r="F111" s="17"/>
-      <c r="G111" s="17"/>
+      <c r="A111" s="16"/>
+      <c r="B111" s="16"/>
+      <c r="C111" s="16"/>
+      <c r="D111" s="16"/>
+      <c r="E111" s="16"/>
+      <c r="F111" s="16"/>
+      <c r="G111" s="16"/>
     </row>
     <row r="112" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="17"/>
-      <c r="B112" s="17"/>
-      <c r="C112" s="17"/>
-      <c r="D112" s="17"/>
-      <c r="E112" s="17"/>
-      <c r="F112" s="17"/>
-      <c r="G112" s="17"/>
+      <c r="A112" s="16"/>
+      <c r="B112" s="16"/>
+      <c r="C112" s="16"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="16"/>
+      <c r="F112" s="16"/>
+      <c r="G112" s="16"/>
     </row>
     <row r="113" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="17"/>
-      <c r="B113" s="17"/>
-      <c r="C113" s="17"/>
-      <c r="D113" s="17"/>
-      <c r="E113" s="17"/>
-      <c r="F113" s="17"/>
-      <c r="G113" s="17"/>
+      <c r="A113" s="16"/>
+      <c r="B113" s="16"/>
+      <c r="C113" s="16"/>
+      <c r="D113" s="16"/>
+      <c r="E113" s="16"/>
+      <c r="F113" s="16"/>
+      <c r="G113" s="16"/>
     </row>
     <row r="114" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="17"/>
-      <c r="B114" s="17"/>
-      <c r="C114" s="17"/>
-      <c r="D114" s="17"/>
-      <c r="E114" s="17"/>
-      <c r="F114" s="17"/>
-      <c r="G114" s="17"/>
+      <c r="A114" s="16"/>
+      <c r="B114" s="16"/>
+      <c r="C114" s="16"/>
+      <c r="D114" s="16"/>
+      <c r="E114" s="16"/>
+      <c r="F114" s="16"/>
+      <c r="G114" s="16"/>
     </row>
     <row r="115" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="17"/>
-      <c r="B115" s="17"/>
-      <c r="C115" s="17"/>
-      <c r="D115" s="17"/>
-      <c r="E115" s="17"/>
-      <c r="F115" s="17"/>
-      <c r="G115" s="17"/>
+      <c r="A115" s="16"/>
+      <c r="B115" s="16"/>
+      <c r="C115" s="16"/>
+      <c r="D115" s="16"/>
+      <c r="E115" s="16"/>
+      <c r="F115" s="16"/>
+      <c r="G115" s="16"/>
     </row>
     <row r="116" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="17"/>
-      <c r="B116" s="17"/>
-      <c r="C116" s="17"/>
-      <c r="D116" s="17"/>
-      <c r="E116" s="17"/>
-      <c r="F116" s="17"/>
-      <c r="G116" s="17"/>
+      <c r="A116" s="16"/>
+      <c r="B116" s="16"/>
+      <c r="C116" s="16"/>
+      <c r="D116" s="16"/>
+      <c r="E116" s="16"/>
+      <c r="F116" s="16"/>
+      <c r="G116" s="16"/>
     </row>
     <row r="117" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="17"/>
-      <c r="B117" s="17"/>
-      <c r="C117" s="17"/>
-      <c r="D117" s="17"/>
-      <c r="E117" s="17"/>
-      <c r="F117" s="17"/>
-      <c r="G117" s="17"/>
+      <c r="A117" s="16"/>
+      <c r="B117" s="16"/>
+      <c r="C117" s="16"/>
+      <c r="D117" s="16"/>
+      <c r="E117" s="16"/>
+      <c r="F117" s="16"/>
+      <c r="G117" s="16"/>
     </row>
     <row r="118" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="17"/>
-      <c r="B118" s="17"/>
-      <c r="C118" s="17"/>
-      <c r="D118" s="17"/>
-      <c r="E118" s="17"/>
-      <c r="F118" s="17"/>
-      <c r="G118" s="17"/>
+      <c r="A118" s="16"/>
+      <c r="B118" s="16"/>
+      <c r="C118" s="16"/>
+      <c r="D118" s="16"/>
+      <c r="E118" s="16"/>
+      <c r="F118" s="16"/>
+      <c r="G118" s="16"/>
     </row>
     <row r="119" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="17"/>
-      <c r="B119" s="17"/>
-      <c r="C119" s="17"/>
-      <c r="D119" s="17"/>
-      <c r="E119" s="17"/>
-      <c r="F119" s="17"/>
-      <c r="G119" s="17"/>
+      <c r="A119" s="16"/>
+      <c r="B119" s="16"/>
+      <c r="C119" s="16"/>
+      <c r="D119" s="16"/>
+      <c r="E119" s="16"/>
+      <c r="F119" s="16"/>
+      <c r="G119" s="16"/>
     </row>
     <row r="120" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="17"/>
-      <c r="B120" s="17"/>
-      <c r="C120" s="17"/>
-      <c r="D120" s="17"/>
-      <c r="E120" s="17"/>
-      <c r="F120" s="17"/>
-      <c r="G120" s="17"/>
+      <c r="A120" s="16"/>
+      <c r="B120" s="16"/>
+      <c r="C120" s="16"/>
+      <c r="D120" s="16"/>
+      <c r="E120" s="16"/>
+      <c r="F120" s="16"/>
+      <c r="G120" s="16"/>
     </row>
     <row r="121" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="17"/>
-      <c r="B121" s="17"/>
-      <c r="C121" s="17"/>
-      <c r="D121" s="17"/>
-      <c r="E121" s="17"/>
-      <c r="F121" s="17"/>
-      <c r="G121" s="17"/>
+      <c r="A121" s="16"/>
+      <c r="B121" s="16"/>
+      <c r="C121" s="16"/>
+      <c r="D121" s="16"/>
+      <c r="E121" s="16"/>
+      <c r="F121" s="16"/>
+      <c r="G121" s="16"/>
     </row>
     <row r="122" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="51" t="s">
+      <c r="A122" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="B122" s="51"/>
-      <c r="C122" s="51"/>
-      <c r="D122" s="51"/>
-      <c r="E122" s="51"/>
-      <c r="F122" s="17"/>
-      <c r="G122" s="17"/>
+      <c r="B122" s="23"/>
+      <c r="C122" s="23"/>
+      <c r="D122" s="23"/>
+      <c r="E122" s="23"/>
+      <c r="F122" s="16"/>
+      <c r="G122" s="16"/>
     </row>
     <row r="123" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="50" t="s">
+      <c r="A123" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="B123" s="50"/>
-      <c r="C123" s="50"/>
-      <c r="D123" s="50"/>
-      <c r="E123" s="50"/>
-      <c r="F123" s="17"/>
-      <c r="G123" s="17"/>
+      <c r="B123" s="39"/>
+      <c r="C123" s="39"/>
+      <c r="D123" s="39"/>
+      <c r="E123" s="39"/>
+      <c r="F123" s="16"/>
+      <c r="G123" s="16"/>
     </row>
     <row r="124" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="50" t="s">
+      <c r="A124" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="B124" s="50"/>
-      <c r="C124" s="50"/>
-      <c r="D124" s="50"/>
-      <c r="E124" s="50"/>
-      <c r="F124" s="17"/>
-      <c r="G124" s="17"/>
+      <c r="B124" s="39"/>
+      <c r="C124" s="39"/>
+      <c r="D124" s="39"/>
+      <c r="E124" s="39"/>
+      <c r="F124" s="16"/>
+      <c r="G124" s="16"/>
     </row>
     <row r="125" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="22" t="s">
+      <c r="A125" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="B125" s="22"/>
-      <c r="C125" s="22"/>
-      <c r="D125" s="22"/>
-      <c r="E125" s="22"/>
-      <c r="F125" s="17"/>
-      <c r="G125" s="17"/>
+      <c r="B125" s="37"/>
+      <c r="C125" s="37"/>
+      <c r="D125" s="37"/>
+      <c r="E125" s="37"/>
+      <c r="F125" s="16"/>
+      <c r="G125" s="16"/>
     </row>
     <row r="126" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="13" t="s">
+      <c r="A126" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B126" s="27" t="s">
+      <c r="B126" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="C126" s="27"/>
-      <c r="D126" s="27"/>
-      <c r="E126" s="13" t="s">
+      <c r="C126" s="38"/>
+      <c r="D126" s="38"/>
+      <c r="E126" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F126" s="27" t="s">
+      <c r="F126" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="G126" s="27"/>
+      <c r="G126" s="38"/>
     </row>
     <row r="127" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="6">
+      <c r="A127" s="5">
         <v>1</v>
       </c>
-      <c r="B127" s="41" t="s">
+      <c r="B127" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="C127" s="42"/>
-      <c r="D127" s="43"/>
-      <c r="E127" s="6"/>
-      <c r="F127" s="41"/>
-      <c r="G127" s="43"/>
+      <c r="C127" s="35"/>
+      <c r="D127" s="36"/>
+      <c r="E127" s="5"/>
+      <c r="F127" s="34"/>
+      <c r="G127" s="36"/>
     </row>
     <row r="128" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="6">
+      <c r="A128" s="5">
         <v>2</v>
       </c>
-      <c r="B128" s="41" t="s">
+      <c r="B128" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="C128" s="42"/>
-      <c r="D128" s="43"/>
-      <c r="E128" s="6"/>
-      <c r="F128" s="41"/>
-      <c r="G128" s="43"/>
+      <c r="C128" s="35"/>
+      <c r="D128" s="36"/>
+      <c r="E128" s="5"/>
+      <c r="F128" s="34"/>
+      <c r="G128" s="36"/>
     </row>
     <row r="129" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="6">
+      <c r="A129" s="5">
         <v>3</v>
       </c>
-      <c r="B129" s="41" t="s">
+      <c r="B129" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="C129" s="42"/>
-      <c r="D129" s="43"/>
-      <c r="E129" s="6"/>
-      <c r="F129" s="41" t="s">
+      <c r="C129" s="35"/>
+      <c r="D129" s="36"/>
+      <c r="E129" s="5"/>
+      <c r="F129" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="G129" s="43"/>
+      <c r="G129" s="36"/>
     </row>
     <row r="130" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="6">
+      <c r="A130" s="5">
         <v>4</v>
       </c>
-      <c r="B130" s="41" t="s">
+      <c r="B130" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="C130" s="42"/>
-      <c r="D130" s="43"/>
-      <c r="E130" s="6"/>
-      <c r="F130" s="41"/>
-      <c r="G130" s="43"/>
+      <c r="C130" s="35"/>
+      <c r="D130" s="36"/>
+      <c r="E130" s="5"/>
+      <c r="F130" s="34"/>
+      <c r="G130" s="36"/>
     </row>
     <row r="131" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="6">
+      <c r="A131" s="5">
         <v>5</v>
       </c>
-      <c r="B131" s="41" t="s">
+      <c r="B131" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="C131" s="42"/>
-      <c r="D131" s="43"/>
-      <c r="E131" s="6"/>
-      <c r="F131" s="41" t="s">
+      <c r="C131" s="35"/>
+      <c r="D131" s="36"/>
+      <c r="E131" s="5"/>
+      <c r="F131" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="G131" s="43"/>
+      <c r="G131" s="36"/>
     </row>
     <row r="132" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="6">
+      <c r="A132" s="5">
         <v>6</v>
       </c>
-      <c r="B132" s="41" t="s">
+      <c r="B132" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="C132" s="42"/>
-      <c r="D132" s="43"/>
-      <c r="E132" s="6"/>
-      <c r="F132" s="41" t="s">
+      <c r="C132" s="35"/>
+      <c r="D132" s="36"/>
+      <c r="E132" s="5"/>
+      <c r="F132" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="G132" s="43"/>
+      <c r="G132" s="36"/>
     </row>
     <row r="133" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="6">
+      <c r="A133" s="5">
         <v>7</v>
       </c>
-      <c r="B133" s="41" t="s">
+      <c r="B133" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="C133" s="42"/>
-      <c r="D133" s="43"/>
-      <c r="E133" s="6"/>
-      <c r="F133" s="41" t="s">
+      <c r="C133" s="35"/>
+      <c r="D133" s="36"/>
+      <c r="E133" s="5"/>
+      <c r="F133" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="G133" s="43"/>
+      <c r="G133" s="36"/>
     </row>
     <row r="134" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="6">
+      <c r="A134" s="5">
         <v>8</v>
       </c>
-      <c r="B134" s="41" t="s">
+      <c r="B134" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="C134" s="42"/>
-      <c r="D134" s="43"/>
-      <c r="E134" s="6"/>
-      <c r="F134" s="41"/>
-      <c r="G134" s="43"/>
+      <c r="C134" s="35"/>
+      <c r="D134" s="36"/>
+      <c r="E134" s="5"/>
+      <c r="F134" s="34"/>
+      <c r="G134" s="36"/>
     </row>
     <row r="135" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="6">
+      <c r="A135" s="5">
         <v>9</v>
       </c>
-      <c r="B135" s="41" t="s">
+      <c r="B135" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="C135" s="42"/>
-      <c r="D135" s="43"/>
-      <c r="E135" s="6"/>
-      <c r="F135" s="41"/>
-      <c r="G135" s="43"/>
+      <c r="C135" s="35"/>
+      <c r="D135" s="36"/>
+      <c r="E135" s="5"/>
+      <c r="F135" s="34"/>
+      <c r="G135" s="36"/>
     </row>
     <row r="136" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="6">
+      <c r="A136" s="5">
         <v>10</v>
       </c>
-      <c r="B136" s="41" t="s">
+      <c r="B136" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="C136" s="42"/>
-      <c r="D136" s="43"/>
-      <c r="E136" s="6"/>
-      <c r="F136" s="41"/>
-      <c r="G136" s="43"/>
+      <c r="C136" s="35"/>
+      <c r="D136" s="36"/>
+      <c r="E136" s="5"/>
+      <c r="F136" s="34"/>
+      <c r="G136" s="36"/>
     </row>
     <row r="137" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="6">
+      <c r="A137" s="5">
         <v>11</v>
       </c>
-      <c r="B137" s="41" t="s">
+      <c r="B137" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="C137" s="42"/>
-      <c r="D137" s="43"/>
-      <c r="E137" s="6"/>
-      <c r="F137" s="41"/>
-      <c r="G137" s="43"/>
+      <c r="C137" s="35"/>
+      <c r="D137" s="36"/>
+      <c r="E137" s="5"/>
+      <c r="F137" s="34"/>
+      <c r="G137" s="36"/>
     </row>
     <row r="138" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="7"/>
-      <c r="B138" s="18"/>
-      <c r="C138" s="18"/>
-      <c r="D138" s="18"/>
-      <c r="E138" s="7"/>
-      <c r="F138" s="18"/>
-      <c r="G138" s="18"/>
+      <c r="A138" s="6"/>
+      <c r="B138" s="17"/>
+      <c r="C138" s="17"/>
+      <c r="D138" s="17"/>
+      <c r="E138" s="6"/>
+      <c r="F138" s="17"/>
+      <c r="G138" s="17"/>
     </row>
     <row r="139" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="17"/>
-      <c r="B139" s="17"/>
-      <c r="C139" s="17"/>
-      <c r="D139" s="17"/>
-      <c r="E139" s="17"/>
-      <c r="F139" s="17"/>
-      <c r="G139" s="17"/>
+      <c r="A139" s="16"/>
+      <c r="B139" s="16"/>
+      <c r="C139" s="16"/>
+      <c r="D139" s="16"/>
+      <c r="E139" s="16"/>
+      <c r="F139" s="16"/>
+      <c r="G139" s="16"/>
     </row>
     <row r="140" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="51" t="s">
+      <c r="A140" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="B140" s="51"/>
-      <c r="C140" s="51"/>
-      <c r="D140" s="51"/>
-      <c r="E140" s="51"/>
-      <c r="F140" s="17"/>
-      <c r="G140" s="17"/>
+      <c r="B140" s="23"/>
+      <c r="C140" s="23"/>
+      <c r="D140" s="23"/>
+      <c r="E140" s="23"/>
+      <c r="F140" s="16"/>
+      <c r="G140" s="16"/>
     </row>
     <row r="141" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="19" t="s">
+      <c r="A141" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="B141" s="19" t="s">
+      <c r="B141" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="C141" s="19" t="s">
+      <c r="C141" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="D141" s="19" t="s">
+      <c r="D141" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="E141" s="19" t="s">
+      <c r="E141" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="F141" s="23" t="s">
+      <c r="F141" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="G141" s="23"/>
+      <c r="G141" s="24"/>
     </row>
     <row r="142" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="20"/>
-      <c r="B142" s="20"/>
-      <c r="C142" s="20"/>
-      <c r="D142" s="20"/>
-      <c r="E142" s="20"/>
-      <c r="F142" s="44"/>
-      <c r="G142" s="44"/>
+      <c r="A142" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="B142" s="21"/>
+      <c r="C142" s="21"/>
+      <c r="D142" s="21"/>
+      <c r="E142" s="21"/>
+      <c r="F142" s="51"/>
+      <c r="G142" s="51"/>
     </row>
     <row r="143" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="17"/>
-      <c r="B143" s="17"/>
-      <c r="C143" s="17"/>
-      <c r="D143" s="17"/>
-      <c r="E143" s="17"/>
-      <c r="F143" s="17"/>
-      <c r="G143" s="17"/>
+      <c r="A143" s="16"/>
+      <c r="B143" s="16"/>
+      <c r="C143" s="16"/>
+      <c r="D143" s="16"/>
+      <c r="E143" s="16"/>
+      <c r="F143" s="16"/>
+      <c r="G143" s="16"/>
     </row>
     <row r="144" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="17"/>
-      <c r="B144" s="17"/>
-      <c r="C144" s="17"/>
-      <c r="D144" s="17"/>
-      <c r="E144" s="17"/>
-      <c r="F144" s="17"/>
-      <c r="G144" s="17"/>
+      <c r="A144" s="16"/>
+      <c r="B144" s="16"/>
+      <c r="C144" s="16"/>
+      <c r="D144" s="16"/>
+      <c r="E144" s="16"/>
+      <c r="F144" s="16"/>
+      <c r="G144" s="16"/>
     </row>
     <row r="145" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="17"/>
-      <c r="B145" s="17"/>
-      <c r="C145" s="17"/>
-      <c r="D145" s="17"/>
-      <c r="E145" s="17"/>
-      <c r="F145" s="17"/>
-      <c r="G145" s="17"/>
+      <c r="A145" s="16"/>
+      <c r="B145" s="16"/>
+      <c r="C145" s="16"/>
+      <c r="D145" s="16"/>
+      <c r="E145" s="16"/>
+      <c r="F145" s="16"/>
+      <c r="G145" s="16"/>
     </row>
     <row r="146" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="17"/>
-      <c r="B146" s="17"/>
-      <c r="C146" s="17"/>
-      <c r="D146" s="17"/>
-      <c r="E146" s="17"/>
-      <c r="F146" s="17"/>
-      <c r="G146" s="17"/>
+      <c r="A146" s="16"/>
+      <c r="B146" s="16"/>
+      <c r="C146" s="16"/>
+      <c r="D146" s="16"/>
+      <c r="E146" s="16"/>
+      <c r="F146" s="16"/>
+      <c r="G146" s="16"/>
     </row>
     <row r="147" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="17"/>
-      <c r="B147" s="17"/>
-      <c r="C147" s="17"/>
-      <c r="D147" s="17"/>
-      <c r="E147" s="17"/>
-      <c r="F147" s="17"/>
-      <c r="G147" s="17"/>
+      <c r="A147" s="16"/>
+      <c r="B147" s="16"/>
+      <c r="C147" s="16"/>
+      <c r="D147" s="16"/>
+      <c r="E147" s="16"/>
+      <c r="F147" s="16"/>
+      <c r="G147" s="16"/>
     </row>
     <row r="148" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="17"/>
-      <c r="B148" s="17"/>
-      <c r="C148" s="17"/>
-      <c r="D148" s="17"/>
-      <c r="E148" s="17"/>
-      <c r="F148" s="17"/>
-      <c r="G148" s="17"/>
+      <c r="A148" s="16"/>
+      <c r="B148" s="16"/>
+      <c r="C148" s="16"/>
+      <c r="D148" s="16"/>
+      <c r="E148" s="16"/>
+      <c r="F148" s="16"/>
+      <c r="G148" s="16"/>
     </row>
     <row r="149" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="17"/>
-      <c r="B149" s="17"/>
-      <c r="C149" s="17"/>
-      <c r="D149" s="17"/>
-      <c r="E149" s="17"/>
-      <c r="F149" s="17"/>
-      <c r="G149" s="17"/>
+      <c r="A149" s="16"/>
+      <c r="B149" s="16"/>
+      <c r="C149" s="16"/>
+      <c r="D149" s="16"/>
+      <c r="E149" s="16"/>
+      <c r="F149" s="16"/>
+      <c r="G149" s="16"/>
     </row>
     <row r="150" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="17"/>
-      <c r="B150" s="17"/>
-      <c r="C150" s="17"/>
-      <c r="D150" s="17"/>
-      <c r="E150" s="17"/>
-      <c r="F150" s="17"/>
-      <c r="G150" s="17"/>
+      <c r="A150" s="16"/>
+      <c r="B150" s="16"/>
+      <c r="C150" s="16"/>
+      <c r="D150" s="16"/>
+      <c r="E150" s="16"/>
+      <c r="F150" s="16"/>
+      <c r="G150" s="16"/>
     </row>
     <row r="151" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="17"/>
-      <c r="B151" s="17"/>
-      <c r="C151" s="17"/>
-      <c r="D151" s="17"/>
-      <c r="E151" s="17"/>
-      <c r="F151" s="17"/>
-      <c r="G151" s="17"/>
+      <c r="A151" s="16"/>
+      <c r="B151" s="16"/>
+      <c r="C151" s="16"/>
+      <c r="D151" s="16"/>
+      <c r="E151" s="16"/>
+      <c r="F151" s="16"/>
+      <c r="G151" s="16"/>
     </row>
     <row r="152" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="17"/>
-      <c r="B152" s="17"/>
-      <c r="C152" s="17"/>
-      <c r="D152" s="17"/>
-      <c r="E152" s="17"/>
-      <c r="F152" s="17"/>
-      <c r="G152" s="17"/>
+      <c r="A152" s="16"/>
+      <c r="B152" s="16"/>
+      <c r="C152" s="16"/>
+      <c r="D152" s="16"/>
+      <c r="E152" s="16"/>
+      <c r="F152" s="16"/>
+      <c r="G152" s="16"/>
     </row>
     <row r="153" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="17"/>
-      <c r="B153" s="17"/>
-      <c r="C153" s="17"/>
-      <c r="D153" s="17"/>
-      <c r="E153" s="17"/>
-      <c r="F153" s="17"/>
-      <c r="G153" s="17"/>
+      <c r="A153" s="16"/>
+      <c r="B153" s="16"/>
+      <c r="C153" s="16"/>
+      <c r="D153" s="16"/>
+      <c r="E153" s="16"/>
+      <c r="F153" s="16"/>
+      <c r="G153" s="16"/>
     </row>
     <row r="154" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="17"/>
-      <c r="B154" s="17"/>
-      <c r="C154" s="17"/>
-      <c r="D154" s="17"/>
-      <c r="E154" s="17"/>
-      <c r="F154" s="17"/>
-      <c r="G154" s="17"/>
+      <c r="A154" s="16"/>
+      <c r="B154" s="16"/>
+      <c r="C154" s="16"/>
+      <c r="D154" s="16"/>
+      <c r="E154" s="16"/>
+      <c r="F154" s="16"/>
+      <c r="G154" s="16"/>
     </row>
     <row r="155" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="17"/>
-      <c r="B155" s="17"/>
-      <c r="C155" s="17"/>
-      <c r="D155" s="17"/>
-      <c r="E155" s="17"/>
-      <c r="F155" s="17"/>
-      <c r="G155" s="17"/>
+      <c r="A155" s="16"/>
+      <c r="B155" s="16"/>
+      <c r="C155" s="16"/>
+      <c r="D155" s="16"/>
+      <c r="E155" s="16"/>
+      <c r="F155" s="16"/>
+      <c r="G155" s="16"/>
     </row>
     <row r="156" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="17"/>
-      <c r="B156" s="17"/>
-      <c r="C156" s="17"/>
-      <c r="D156" s="17"/>
-      <c r="E156" s="17"/>
-      <c r="F156" s="17"/>
-      <c r="G156" s="17"/>
+      <c r="A156" s="16"/>
+      <c r="B156" s="16"/>
+      <c r="C156" s="16"/>
+      <c r="D156" s="16"/>
+      <c r="E156" s="16"/>
+      <c r="F156" s="16"/>
+      <c r="G156" s="16"/>
     </row>
     <row r="157" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="17"/>
-      <c r="B157" s="17"/>
-      <c r="C157" s="17"/>
-      <c r="D157" s="17"/>
-      <c r="E157" s="17"/>
-      <c r="F157" s="17"/>
-      <c r="G157" s="17"/>
+      <c r="A157" s="16"/>
+      <c r="B157" s="16"/>
+      <c r="C157" s="16"/>
+      <c r="D157" s="16"/>
+      <c r="E157" s="16"/>
+      <c r="F157" s="16"/>
+      <c r="G157" s="16"/>
     </row>
     <row r="158" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="17"/>
-      <c r="B158" s="17"/>
-      <c r="C158" s="17"/>
-      <c r="D158" s="17"/>
-      <c r="E158" s="17"/>
-      <c r="F158" s="17"/>
-      <c r="G158" s="17"/>
+      <c r="A158" s="16"/>
+      <c r="B158" s="16"/>
+      <c r="C158" s="16"/>
+      <c r="D158" s="16"/>
+      <c r="E158" s="16"/>
+      <c r="F158" s="16"/>
+      <c r="G158" s="16"/>
     </row>
     <row r="159" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="17"/>
-      <c r="B159" s="17"/>
-      <c r="C159" s="17"/>
-      <c r="D159" s="17"/>
-      <c r="E159" s="17"/>
-      <c r="F159" s="17"/>
-      <c r="G159" s="17"/>
+      <c r="A159" s="16"/>
+      <c r="B159" s="16"/>
+      <c r="C159" s="16"/>
+      <c r="D159" s="16"/>
+      <c r="E159" s="16"/>
+      <c r="F159" s="16"/>
+      <c r="G159" s="16"/>
     </row>
     <row r="160" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="17"/>
-      <c r="B160" s="17"/>
-      <c r="C160" s="17"/>
-      <c r="D160" s="17"/>
-      <c r="E160" s="17"/>
-      <c r="F160" s="17"/>
-      <c r="G160" s="17"/>
+      <c r="A160" s="16"/>
+      <c r="B160" s="16"/>
+      <c r="C160" s="16"/>
+      <c r="D160" s="16"/>
+      <c r="E160" s="16"/>
+      <c r="F160" s="16"/>
+      <c r="G160" s="16"/>
     </row>
     <row r="161" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="17"/>
-      <c r="B161" s="17"/>
-      <c r="C161" s="17"/>
-      <c r="D161" s="17"/>
-      <c r="E161" s="17"/>
-      <c r="F161" s="17"/>
-      <c r="G161" s="17"/>
+      <c r="A161" s="16"/>
+      <c r="B161" s="16"/>
+      <c r="C161" s="16"/>
+      <c r="D161" s="16"/>
+      <c r="E161" s="16"/>
+      <c r="F161" s="16"/>
+      <c r="G161" s="16"/>
     </row>
     <row r="162" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="51" t="s">
+      <c r="A162" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="B162" s="51"/>
-      <c r="C162" s="51"/>
-      <c r="D162" s="51"/>
-      <c r="E162" s="51"/>
-      <c r="F162" s="17"/>
-      <c r="G162" s="17"/>
+      <c r="B162" s="23"/>
+      <c r="C162" s="23"/>
+      <c r="D162" s="23"/>
+      <c r="E162" s="23"/>
+      <c r="F162" s="16"/>
+      <c r="G162" s="16"/>
     </row>
     <row r="163" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="23" t="s">
+      <c r="A163" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="B163" s="23"/>
-      <c r="C163" s="23"/>
-      <c r="D163" s="23" t="s">
+      <c r="B163" s="24"/>
+      <c r="C163" s="24"/>
+      <c r="D163" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="E163" s="23"/>
-      <c r="F163" s="23"/>
-      <c r="G163" s="17"/>
+      <c r="E163" s="24"/>
+      <c r="F163" s="24"/>
+      <c r="G163" s="16"/>
     </row>
     <row r="164" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="26"/>
-      <c r="B164" s="26"/>
-      <c r="C164" s="26"/>
-      <c r="D164" s="26"/>
-      <c r="E164" s="26"/>
-      <c r="F164" s="26"/>
-      <c r="G164" s="17"/>
+      <c r="A164" s="51"/>
+      <c r="B164" s="51"/>
+      <c r="C164" s="51"/>
+      <c r="D164" s="51"/>
+      <c r="E164" s="51"/>
+      <c r="F164" s="51"/>
+      <c r="G164" s="16"/>
     </row>
     <row r="165" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="17"/>
-      <c r="B165" s="17"/>
-      <c r="C165" s="17"/>
-      <c r="D165" s="17"/>
-      <c r="E165" s="17"/>
-      <c r="F165" s="17"/>
-      <c r="G165" s="17"/>
+      <c r="A165" s="16"/>
+      <c r="B165" s="16"/>
+      <c r="C165" s="16"/>
+      <c r="D165" s="16"/>
+      <c r="E165" s="16"/>
+      <c r="F165" s="16"/>
+      <c r="G165" s="16"/>
     </row>
     <row r="166" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="17"/>
-      <c r="B166" s="17"/>
-      <c r="C166" s="17"/>
-      <c r="D166" s="17"/>
-      <c r="E166" s="17"/>
-      <c r="F166" s="17"/>
-      <c r="G166" s="17"/>
+      <c r="A166" s="16"/>
+      <c r="B166" s="16"/>
+      <c r="C166" s="16"/>
+      <c r="D166" s="16"/>
+      <c r="E166" s="16"/>
+      <c r="F166" s="16"/>
+      <c r="G166" s="16"/>
     </row>
     <row r="167" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="51" t="s">
+      <c r="A167" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="B167" s="51"/>
-      <c r="C167" s="51"/>
-      <c r="D167" s="51"/>
-      <c r="E167" s="51"/>
-      <c r="F167" s="17"/>
-      <c r="G167" s="17"/>
+      <c r="B167" s="23"/>
+      <c r="C167" s="23"/>
+      <c r="D167" s="23"/>
+      <c r="E167" s="23"/>
+      <c r="F167" s="16"/>
+      <c r="G167" s="16"/>
     </row>
     <row r="168" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="19" t="s">
+      <c r="A168" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="B168" s="23" t="s">
+      <c r="B168" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="C168" s="23"/>
-      <c r="D168" s="19" t="s">
+      <c r="C168" s="24"/>
+      <c r="D168" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="E168" s="19" t="s">
+      <c r="E168" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F168" s="23" t="s">
+      <c r="F168" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="G168" s="23"/>
+      <c r="G168" s="24"/>
     </row>
     <row r="169" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="20" t="s">
+      <c r="A169" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="B169" s="24"/>
-      <c r="C169" s="25"/>
-      <c r="D169" s="20"/>
-      <c r="E169" s="20"/>
-      <c r="F169" s="24"/>
-      <c r="G169" s="25"/>
+      <c r="B169" s="32"/>
+      <c r="C169" s="33"/>
+      <c r="D169" s="19"/>
+      <c r="E169" s="19"/>
+      <c r="F169" s="32"/>
+      <c r="G169" s="33"/>
     </row>
     <row r="170" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="20" t="s">
+      <c r="A170" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="B170" s="24"/>
-      <c r="C170" s="25"/>
-      <c r="D170" s="20"/>
-      <c r="E170" s="20"/>
-      <c r="F170" s="24"/>
-      <c r="G170" s="25"/>
+      <c r="B170" s="32"/>
+      <c r="C170" s="33"/>
+      <c r="D170" s="19"/>
+      <c r="E170" s="19"/>
+      <c r="F170" s="32"/>
+      <c r="G170" s="33"/>
     </row>
     <row r="171" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A171" s="20" t="s">
+      <c r="A171" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="B171" s="24"/>
-      <c r="C171" s="25"/>
-      <c r="D171" s="20"/>
-      <c r="E171" s="20"/>
-      <c r="F171" s="24"/>
-      <c r="G171" s="25"/>
+      <c r="B171" s="32"/>
+      <c r="C171" s="33"/>
+      <c r="D171" s="19"/>
+      <c r="E171" s="19"/>
+      <c r="F171" s="32"/>
+      <c r="G171" s="33"/>
     </row>
     <row r="172" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="20" t="s">
+      <c r="A172" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="B172" s="24"/>
-      <c r="C172" s="25"/>
-      <c r="D172" s="20"/>
-      <c r="E172" s="20"/>
-      <c r="F172" s="24"/>
-      <c r="G172" s="25"/>
+      <c r="B172" s="32"/>
+      <c r="C172" s="33"/>
+      <c r="D172" s="19"/>
+      <c r="E172" s="19"/>
+      <c r="F172" s="32"/>
+      <c r="G172" s="33"/>
     </row>
     <row r="173" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="17"/>
-      <c r="B173" s="17"/>
-      <c r="C173" s="17"/>
-      <c r="D173" s="17"/>
-      <c r="E173" s="17"/>
-      <c r="F173" s="17"/>
-      <c r="G173" s="17"/>
+      <c r="A173" s="16"/>
+      <c r="B173" s="16"/>
+      <c r="C173" s="16"/>
+      <c r="D173" s="16"/>
+      <c r="E173" s="16"/>
+      <c r="F173" s="16"/>
+      <c r="G173" s="16"/>
     </row>
     <row r="174" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="17"/>
-      <c r="B174" s="17"/>
-      <c r="C174" s="17"/>
-      <c r="D174" s="17"/>
-      <c r="E174" s="17"/>
-      <c r="F174" s="17"/>
-      <c r="G174" s="17"/>
+      <c r="A174" s="16"/>
+      <c r="B174" s="16"/>
+      <c r="C174" s="16"/>
+      <c r="D174" s="16"/>
+      <c r="E174" s="16"/>
+      <c r="F174" s="16"/>
+      <c r="G174" s="16"/>
     </row>
     <row r="175" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="51" t="s">
+      <c r="A175" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="B175" s="51"/>
-      <c r="C175" s="51"/>
-      <c r="D175" s="51"/>
-      <c r="E175" s="51"/>
-      <c r="F175" s="17"/>
-      <c r="G175" s="17"/>
+      <c r="B175" s="23"/>
+      <c r="C175" s="23"/>
+      <c r="D175" s="23"/>
+      <c r="E175" s="23"/>
+      <c r="F175" s="16"/>
+      <c r="G175" s="16"/>
     </row>
     <row r="176" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="23" t="s">
+      <c r="A176" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="B176" s="23"/>
-      <c r="C176" s="23" t="s">
+      <c r="B176" s="24"/>
+      <c r="C176" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="D176" s="23"/>
-      <c r="E176" s="23" t="s">
+      <c r="D176" s="24"/>
+      <c r="E176" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="F176" s="23"/>
-      <c r="G176" s="17"/>
+      <c r="F176" s="24"/>
+      <c r="G176" s="16"/>
     </row>
     <row r="177" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="24" t="s">
+      <c r="A177" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="B177" s="25"/>
-      <c r="C177" s="24"/>
-      <c r="D177" s="25"/>
-      <c r="E177" s="24"/>
-      <c r="F177" s="25"/>
-      <c r="G177" s="17"/>
+      <c r="B177" s="33"/>
+      <c r="C177" s="32"/>
+      <c r="D177" s="33"/>
+      <c r="E177" s="32"/>
+      <c r="F177" s="33"/>
+      <c r="G177" s="16"/>
     </row>
     <row r="178" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="24" t="s">
+      <c r="A178" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="B178" s="25"/>
-      <c r="C178" s="24"/>
-      <c r="D178" s="25"/>
-      <c r="E178" s="24"/>
-      <c r="F178" s="25"/>
-      <c r="G178" s="17"/>
+      <c r="B178" s="33"/>
+      <c r="C178" s="32"/>
+      <c r="D178" s="33"/>
+      <c r="E178" s="32"/>
+      <c r="F178" s="33"/>
+      <c r="G178" s="16"/>
     </row>
     <row r="179" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="24" t="s">
+      <c r="A179" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="B179" s="25"/>
-      <c r="C179" s="24"/>
-      <c r="D179" s="25"/>
-      <c r="E179" s="24"/>
-      <c r="F179" s="25"/>
-      <c r="G179" s="17"/>
+      <c r="B179" s="33"/>
+      <c r="C179" s="32"/>
+      <c r="D179" s="33"/>
+      <c r="E179" s="32"/>
+      <c r="F179" s="33"/>
+      <c r="G179" s="16"/>
     </row>
     <row r="180" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="17"/>
-      <c r="B180" s="17"/>
-      <c r="C180" s="17"/>
-      <c r="D180" s="17"/>
-      <c r="E180" s="17"/>
-      <c r="F180" s="17"/>
-      <c r="G180" s="17"/>
+      <c r="A180" s="16"/>
+      <c r="B180" s="16"/>
+      <c r="C180" s="16"/>
+      <c r="D180" s="16"/>
+      <c r="E180" s="16"/>
+      <c r="F180" s="16"/>
+      <c r="G180" s="16"/>
     </row>
     <row r="181" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="17"/>
-      <c r="B181" s="17"/>
-      <c r="C181" s="17"/>
-      <c r="D181" s="17"/>
-      <c r="E181" s="17"/>
-      <c r="F181" s="17"/>
-      <c r="G181" s="17"/>
+      <c r="A181" s="16"/>
+      <c r="B181" s="16"/>
+      <c r="C181" s="16"/>
+      <c r="D181" s="16"/>
+      <c r="E181" s="16"/>
+      <c r="F181" s="16"/>
+      <c r="G181" s="16"/>
     </row>
     <row r="182" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="51" t="s">
+      <c r="A182" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="B182" s="51"/>
-      <c r="C182" s="51"/>
-      <c r="D182" s="51"/>
-      <c r="E182" s="51"/>
-      <c r="F182" s="17"/>
-      <c r="G182" s="17"/>
+      <c r="B182" s="23"/>
+      <c r="C182" s="23"/>
+      <c r="D182" s="23"/>
+      <c r="E182" s="23"/>
+      <c r="F182" s="16"/>
+      <c r="G182" s="16"/>
     </row>
     <row r="183" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="23" t="s">
+      <c r="A183" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B183" s="23"/>
-      <c r="C183" s="23"/>
-      <c r="D183" s="23"/>
-      <c r="E183" s="23" t="s">
+      <c r="B183" s="24"/>
+      <c r="C183" s="24"/>
+      <c r="D183" s="24"/>
+      <c r="E183" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="F183" s="23"/>
-      <c r="G183" s="23"/>
+      <c r="F183" s="24"/>
+      <c r="G183" s="24"/>
     </row>
     <row r="184" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="45"/>
-      <c r="B184" s="46"/>
-      <c r="C184" s="46"/>
-      <c r="D184" s="47"/>
-      <c r="E184" s="45"/>
-      <c r="F184" s="46"/>
-      <c r="G184" s="47"/>
+      <c r="A184" s="27"/>
+      <c r="B184" s="28"/>
+      <c r="C184" s="28"/>
+      <c r="D184" s="29"/>
+      <c r="E184" s="27"/>
+      <c r="F184" s="28"/>
+      <c r="G184" s="29"/>
     </row>
     <row r="185" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="21"/>
-      <c r="B185" s="21"/>
-      <c r="C185" s="21"/>
-      <c r="D185" s="21"/>
-      <c r="E185" s="21"/>
-      <c r="F185" s="21"/>
-      <c r="G185" s="21"/>
+      <c r="A185" s="20"/>
+      <c r="B185" s="20"/>
+      <c r="C185" s="20"/>
+      <c r="D185" s="20"/>
+      <c r="E185" s="20"/>
+      <c r="F185" s="20"/>
+      <c r="G185" s="20"/>
     </row>
     <row r="186" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A186" s="21"/>
-      <c r="B186" s="21"/>
-      <c r="C186" s="21"/>
-      <c r="D186" s="21"/>
-      <c r="E186" s="21"/>
-      <c r="F186" s="21"/>
-      <c r="G186" s="21"/>
+      <c r="A186" s="20"/>
+      <c r="B186" s="20"/>
+      <c r="C186" s="20"/>
+      <c r="D186" s="20"/>
+      <c r="E186" s="20"/>
+      <c r="F186" s="20"/>
+      <c r="G186" s="20"/>
     </row>
     <row r="187" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A187" s="21"/>
-      <c r="B187" s="21"/>
-      <c r="C187" s="21"/>
-      <c r="D187" s="21"/>
-      <c r="E187" s="21"/>
-      <c r="F187" s="21"/>
-      <c r="G187" s="21"/>
+      <c r="A187" s="20"/>
+      <c r="B187" s="20"/>
+      <c r="C187" s="20"/>
+      <c r="D187" s="20"/>
+      <c r="E187" s="20"/>
+      <c r="F187" s="20"/>
+      <c r="G187" s="20"/>
     </row>
     <row r="188" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A188" s="21"/>
-      <c r="B188" s="21"/>
-      <c r="C188" s="21"/>
-      <c r="D188" s="21"/>
-      <c r="E188" s="21"/>
-      <c r="F188" s="21"/>
-      <c r="G188" s="21"/>
+      <c r="A188" s="20"/>
+      <c r="B188" s="20"/>
+      <c r="C188" s="20"/>
+      <c r="D188" s="20"/>
+      <c r="E188" s="20"/>
+      <c r="F188" s="20"/>
+      <c r="G188" s="20"/>
     </row>
     <row r="189" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A189" s="21"/>
-      <c r="B189" s="21"/>
-      <c r="C189" s="21"/>
-      <c r="D189" s="21"/>
-      <c r="E189" s="21"/>
-      <c r="F189" s="21"/>
-      <c r="G189" s="21"/>
+      <c r="A189" s="20"/>
+      <c r="B189" s="20"/>
+      <c r="C189" s="20"/>
+      <c r="D189" s="20"/>
+      <c r="E189" s="20"/>
+      <c r="F189" s="20"/>
+      <c r="G189" s="20"/>
     </row>
     <row r="190" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A190" s="21"/>
-      <c r="B190" s="21"/>
-      <c r="C190" s="21"/>
-      <c r="D190" s="21"/>
-      <c r="E190" s="21"/>
-      <c r="F190" s="21"/>
-      <c r="G190" s="21"/>
+      <c r="A190" s="20"/>
+      <c r="B190" s="20"/>
+      <c r="C190" s="20"/>
+      <c r="D190" s="20"/>
+      <c r="E190" s="20"/>
+      <c r="F190" s="20"/>
+      <c r="G190" s="20"/>
     </row>
     <row r="191" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A191" s="21"/>
-      <c r="B191" s="21"/>
-      <c r="C191" s="21"/>
-      <c r="D191" s="21"/>
-      <c r="E191" s="21"/>
-      <c r="F191" s="21"/>
-      <c r="G191" s="21"/>
+      <c r="A191" s="20"/>
+      <c r="B191" s="20"/>
+      <c r="C191" s="20"/>
+      <c r="D191" s="20"/>
+      <c r="E191" s="20"/>
+      <c r="F191" s="20"/>
+      <c r="G191" s="20"/>
     </row>
     <row r="192" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A192" s="21"/>
-      <c r="B192" s="21"/>
-      <c r="C192" s="21"/>
-      <c r="D192" s="21"/>
-      <c r="E192" s="21"/>
-      <c r="F192" s="21"/>
-      <c r="G192" s="21"/>
+      <c r="A192" s="20"/>
+      <c r="B192" s="20"/>
+      <c r="C192" s="20"/>
+      <c r="D192" s="20"/>
+      <c r="E192" s="20"/>
+      <c r="F192" s="20"/>
+      <c r="G192" s="20"/>
     </row>
     <row r="193" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A193" s="21"/>
-      <c r="B193" s="21"/>
-      <c r="C193" s="21"/>
-      <c r="D193" s="21"/>
-      <c r="E193" s="21"/>
-      <c r="F193" s="21"/>
-      <c r="G193" s="21"/>
+      <c r="A193" s="20"/>
+      <c r="B193" s="20"/>
+      <c r="C193" s="20"/>
+      <c r="D193" s="20"/>
+      <c r="E193" s="20"/>
+      <c r="F193" s="20"/>
+      <c r="G193" s="20"/>
     </row>
     <row r="194" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A194" s="17"/>
-      <c r="B194" s="17"/>
-      <c r="C194" s="17"/>
-      <c r="D194" s="17"/>
-      <c r="E194" s="17"/>
-      <c r="F194" s="17"/>
-      <c r="G194" s="17"/>
+      <c r="A194" s="16"/>
+      <c r="B194" s="16"/>
+      <c r="C194" s="16"/>
+      <c r="D194" s="16"/>
+      <c r="E194" s="16"/>
+      <c r="F194" s="16"/>
+      <c r="G194" s="16"/>
     </row>
     <row r="195" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A195" s="17"/>
-      <c r="B195" s="17"/>
-      <c r="C195" s="17"/>
-      <c r="D195" s="17"/>
-      <c r="E195" s="17"/>
-      <c r="F195" s="17"/>
-      <c r="G195" s="17"/>
+      <c r="A195" s="16"/>
+      <c r="B195" s="16"/>
+      <c r="C195" s="16"/>
+      <c r="D195" s="16"/>
+      <c r="E195" s="16"/>
+      <c r="F195" s="16"/>
+      <c r="G195" s="16"/>
     </row>
     <row r="196" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A196" s="17"/>
-      <c r="B196" s="17"/>
-      <c r="C196" s="17"/>
-      <c r="D196" s="17"/>
-      <c r="E196" s="17"/>
-      <c r="F196" s="17"/>
-      <c r="G196" s="17"/>
+      <c r="A196" s="16"/>
+      <c r="B196" s="16"/>
+      <c r="C196" s="16"/>
+      <c r="D196" s="16"/>
+      <c r="E196" s="16"/>
+      <c r="F196" s="16"/>
+      <c r="G196" s="16"/>
     </row>
     <row r="197" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="17"/>
-      <c r="B197" s="17"/>
-      <c r="C197" s="17"/>
-      <c r="D197" s="17"/>
-      <c r="E197" s="17"/>
-      <c r="F197" s="17"/>
-      <c r="G197" s="17"/>
+      <c r="A197" s="16"/>
+      <c r="B197" s="16"/>
+      <c r="C197" s="16"/>
+      <c r="D197" s="16"/>
+      <c r="E197" s="16"/>
+      <c r="F197" s="16"/>
+      <c r="G197" s="16"/>
     </row>
     <row r="198" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="17"/>
-      <c r="B198" s="17"/>
-      <c r="C198" s="17"/>
-      <c r="D198" s="17"/>
-      <c r="E198" s="17"/>
-      <c r="F198" s="17"/>
-      <c r="G198" s="17"/>
+      <c r="A198" s="16"/>
+      <c r="B198" s="16"/>
+      <c r="C198" s="16"/>
+      <c r="D198" s="16"/>
+      <c r="E198" s="16"/>
+      <c r="F198" s="16"/>
+      <c r="G198" s="16"/>
     </row>
     <row r="199" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="17"/>
-      <c r="B199" s="17"/>
-      <c r="C199" s="17"/>
-      <c r="D199" s="17"/>
-      <c r="E199" s="17"/>
-      <c r="F199" s="17"/>
-      <c r="G199" s="17"/>
+      <c r="A199" s="16"/>
+      <c r="B199" s="16"/>
+      <c r="C199" s="16"/>
+      <c r="D199" s="16"/>
+      <c r="E199" s="16"/>
+      <c r="F199" s="16"/>
+      <c r="G199" s="16"/>
     </row>
     <row r="201" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="51" t="s">
+      <c r="A201" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="B201" s="51"/>
-      <c r="C201" s="51"/>
-      <c r="D201" s="51"/>
-      <c r="E201" s="51"/>
+      <c r="B201" s="23"/>
+      <c r="C201" s="23"/>
+      <c r="D201" s="23"/>
+      <c r="E201" s="23"/>
     </row>
     <row r="202" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="2" t="s">
+      <c r="A202" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B202" s="31" t="s">
+      <c r="B202" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="C202" s="31"/>
-      <c r="D202" s="31" t="s">
+      <c r="C202" s="25"/>
+      <c r="D202" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="E202" s="31"/>
-      <c r="F202" s="2" t="s">
+      <c r="E202" s="25"/>
+      <c r="F202" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="G202" s="2" t="s">
+      <c r="G202" s="1" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A203" s="4"/>
-      <c r="B203" s="48"/>
-      <c r="C203" s="49"/>
-      <c r="D203" s="30"/>
-      <c r="E203" s="30"/>
-      <c r="F203" s="4"/>
-      <c r="G203" s="4"/>
+      <c r="A203" s="3"/>
+      <c r="B203" s="30"/>
+      <c r="C203" s="31"/>
+      <c r="D203" s="26"/>
+      <c r="E203" s="26"/>
+      <c r="F203" s="3"/>
+      <c r="G203" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="199">
-    <mergeCell ref="A182:E182"/>
-    <mergeCell ref="A183:D183"/>
-    <mergeCell ref="E183:G183"/>
-    <mergeCell ref="A201:E201"/>
-    <mergeCell ref="B202:C202"/>
-    <mergeCell ref="D202:E202"/>
-    <mergeCell ref="D203:E203"/>
-    <mergeCell ref="A184:D184"/>
-    <mergeCell ref="E184:G184"/>
-    <mergeCell ref="B203:C203"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="F141:G141"/>
-    <mergeCell ref="F142:G142"/>
-    <mergeCell ref="A162:E162"/>
-    <mergeCell ref="C177:D177"/>
-    <mergeCell ref="C178:D178"/>
-    <mergeCell ref="C179:D179"/>
-    <mergeCell ref="E177:F177"/>
-    <mergeCell ref="E178:F178"/>
-    <mergeCell ref="E179:F179"/>
-    <mergeCell ref="A179:B179"/>
-    <mergeCell ref="B133:D133"/>
-    <mergeCell ref="F133:G133"/>
-    <mergeCell ref="B134:D134"/>
-    <mergeCell ref="F134:G134"/>
-    <mergeCell ref="B135:D135"/>
-    <mergeCell ref="F135:G135"/>
-    <mergeCell ref="B136:D136"/>
-    <mergeCell ref="F136:G136"/>
-    <mergeCell ref="B137:D137"/>
-    <mergeCell ref="F137:G137"/>
-    <mergeCell ref="B130:D130"/>
-    <mergeCell ref="F130:G130"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="F106:G106"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="F107:G107"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="F108:G108"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="F109:G109"/>
-    <mergeCell ref="A125:E125"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="E176:F176"/>
+    <mergeCell ref="A177:B177"/>
+    <mergeCell ref="A178:B178"/>
+    <mergeCell ref="F168:G168"/>
+    <mergeCell ref="F169:G169"/>
+    <mergeCell ref="F170:G170"/>
+    <mergeCell ref="F171:G171"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="D83:E83"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="D84:E84"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A7:A16"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:F19"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="B98:D98"/>
+    <mergeCell ref="B99:D99"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="F99:G99"/>
     <mergeCell ref="B131:D131"/>
     <mergeCell ref="F131:G131"/>
     <mergeCell ref="B132:D132"/>
@@ -3713,118 +3797,38 @@
     <mergeCell ref="F128:G128"/>
     <mergeCell ref="B129:D129"/>
     <mergeCell ref="F129:G129"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="B98:D98"/>
-    <mergeCell ref="B99:D99"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="F99:G99"/>
-    <mergeCell ref="A89:E89"/>
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A91:E91"/>
-    <mergeCell ref="B92:D92"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="I6:M6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A7:A16"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:F19"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="A78:D78"/>
-    <mergeCell ref="A82:E82"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A73:E73"/>
-    <mergeCell ref="A74:E74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="F83:G83"/>
-    <mergeCell ref="D83:E83"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="D84:E84"/>
-    <mergeCell ref="D85:E85"/>
-    <mergeCell ref="D86:E86"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="B130:D130"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="F107:G107"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="F108:G108"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="F109:G109"/>
+    <mergeCell ref="A125:E125"/>
+    <mergeCell ref="B133:D133"/>
+    <mergeCell ref="F133:G133"/>
+    <mergeCell ref="B134:D134"/>
+    <mergeCell ref="F134:G134"/>
+    <mergeCell ref="B135:D135"/>
+    <mergeCell ref="F135:G135"/>
+    <mergeCell ref="B136:D136"/>
+    <mergeCell ref="F136:G136"/>
+    <mergeCell ref="B137:D137"/>
+    <mergeCell ref="F137:G137"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="F141:G141"/>
+    <mergeCell ref="F142:G142"/>
+    <mergeCell ref="A162:E162"/>
+    <mergeCell ref="C177:D177"/>
+    <mergeCell ref="C178:D178"/>
+    <mergeCell ref="C179:D179"/>
+    <mergeCell ref="E177:F177"/>
+    <mergeCell ref="E178:F178"/>
+    <mergeCell ref="E179:F179"/>
+    <mergeCell ref="A179:B179"/>
     <mergeCell ref="A163:C163"/>
     <mergeCell ref="D164:F164"/>
     <mergeCell ref="A167:E167"/>
@@ -3838,14 +3842,16 @@
     <mergeCell ref="A164:C164"/>
     <mergeCell ref="A175:E175"/>
     <mergeCell ref="A176:B176"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="E176:F176"/>
-    <mergeCell ref="A177:B177"/>
-    <mergeCell ref="A178:B178"/>
-    <mergeCell ref="F168:G168"/>
-    <mergeCell ref="F169:G169"/>
-    <mergeCell ref="F170:G170"/>
-    <mergeCell ref="F171:G171"/>
+    <mergeCell ref="A182:E182"/>
+    <mergeCell ref="A183:D183"/>
+    <mergeCell ref="E183:G183"/>
+    <mergeCell ref="A201:E201"/>
+    <mergeCell ref="B202:C202"/>
+    <mergeCell ref="D202:E202"/>
+    <mergeCell ref="D203:E203"/>
+    <mergeCell ref="A184:D184"/>
+    <mergeCell ref="E184:G184"/>
+    <mergeCell ref="B203:C203"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/[서버]_FAP_정기점검/templates/server_report_form.xlsx
+++ b/[서버]_FAP_정기점검/templates/server_report_form.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgjan\AppData\Roaming\MobaXterm\slash\mx86_64b\RemoteFiles\1313484_6_53\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgjan\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B3857C-BDF9-438C-9842-5240468F66A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0132AE-5243-4B78-B729-0D0DF69BDC39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="-108" windowWidth="22068" windowHeight="13176" xr2:uid="{F40717F4-5740-4B20-A9D7-5EC8DA815EF1}"/>
+    <workbookView xWindow="29790" yWindow="-120" windowWidth="27930" windowHeight="16440" xr2:uid="{F40717F4-5740-4B20-A9D7-5EC8DA815EF1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="145">
   <si>
     <t>자동화 서버 시스템 통상점검 일지</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -139,9 +139,6 @@
   </si>
   <si>
     <t>Total</t>
-  </si>
-  <si>
-    <t>62G</t>
   </si>
   <si>
     <t>1. CPU, 디스크, 메모리 사용률 점검</t>
@@ -395,34 +392,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>fap-agent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fap-manager</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fap-web</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fap-haproxy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fap-redis</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>portainer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">    2) scsic-falcon2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -564,10 +533,6 @@
   </si>
   <si>
     <t>적용 권한</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시스템 접속 허용 IP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -683,10 +648,6 @@
       </rPr>
       <t>free –h</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>관리자 그룹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -988,16 +949,76 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1013,66 +1034,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1409,7 +1370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05EC5C17-C0F9-4B72-92E2-139A6D8D6DF2}">
-  <dimension ref="A2:M203"/>
+  <dimension ref="A2:M147"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="20.09765625" style="2" customWidth="1"/>
@@ -1429,39 +1390,39 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+    </row>
+    <row r="4" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-    </row>
-    <row r="4" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="25"/>
+      <c r="B4" s="33"/>
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1473,14 +1434,14 @@
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="25"/>
+      <c r="A5" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="33"/>
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
@@ -1492,228 +1453,228 @@
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="26" t="s">
+      <c r="A6" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="36"/>
+      <c r="C6" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
     </row>
     <row r="7" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="42" t="s">
-        <v>45</v>
+      <c r="A7" s="37" t="s">
+        <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
       <c r="G7" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="43"/>
+      <c r="A8" s="38"/>
       <c r="B8" s="3">
         <v>1</v>
       </c>
-      <c r="C8" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
+      <c r="C8" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
       <c r="G8" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="43"/>
+      <c r="A9" s="38"/>
       <c r="B9" s="3">
         <v>2</v>
       </c>
-      <c r="C9" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
+      <c r="C9" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
       <c r="G9" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="43"/>
+      <c r="A10" s="38"/>
       <c r="B10" s="3">
         <v>3</v>
       </c>
-      <c r="C10" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
+      <c r="C10" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
       <c r="G10" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="43"/>
+      <c r="A11" s="38"/>
       <c r="B11" s="3">
         <v>4</v>
       </c>
-      <c r="C11" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
+      <c r="C11" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
       <c r="G11" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="43"/>
+      <c r="A12" s="38"/>
       <c r="B12" s="3">
         <v>5</v>
       </c>
-      <c r="C12" s="49" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
+      <c r="C12" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
       <c r="G12" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="43"/>
+      <c r="A13" s="38"/>
       <c r="B13" s="3">
         <v>6</v>
       </c>
-      <c r="C13" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
+      <c r="C13" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
       <c r="G13" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="43"/>
+      <c r="A14" s="38"/>
       <c r="B14" s="3">
         <v>7</v>
       </c>
-      <c r="C14" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="47"/>
+      <c r="C14" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="42"/>
       <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="43"/>
+      <c r="A15" s="38"/>
       <c r="B15" s="3">
         <v>8</v>
       </c>
-      <c r="C15" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
+      <c r="C15" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
       <c r="G15" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="44"/>
+      <c r="A16" s="39"/>
       <c r="B16" s="3">
         <v>9</v>
       </c>
-      <c r="C16" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="47"/>
+      <c r="C16" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="42"/>
       <c r="G16" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
     </row>
     <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
+      <c r="A18" s="33"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
     </row>
     <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
     </row>
     <row r="22" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="25"/>
+      <c r="C23" s="33"/>
       <c r="D23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="E23" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="25"/>
+      <c r="F23" s="33"/>
       <c r="G23" s="1" t="s">
         <v>15</v>
       </c>
@@ -1722,38 +1683,38 @@
       <c r="A24" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="48"/>
+      <c r="B24" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="27"/>
       <c r="D24" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="48" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" s="48"/>
+      <c r="F24" s="27"/>
       <c r="G24" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="48"/>
+      <c r="B25" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="27"/>
       <c r="D25" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="48" t="s">
-        <v>63</v>
-      </c>
-      <c r="F25" s="48"/>
+      <c r="E25" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="27"/>
       <c r="G25" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -1766,176 +1727,176 @@
     </row>
     <row r="28" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="B29" s="25" t="s">
+      <c r="C29" s="33"/>
+      <c r="D29" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25" t="s">
+      <c r="E29" s="33"/>
+      <c r="F29" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="G29" s="25"/>
+      <c r="G29" s="33"/>
     </row>
     <row r="30" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B30" s="48"/>
-      <c r="C30" s="48"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="48"/>
+        <v>68</v>
+      </c>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
     </row>
     <row r="31" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="48"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
+        <v>69</v>
+      </c>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
     </row>
     <row r="32" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" s="48"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
+        <v>70</v>
+      </c>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
     </row>
     <row r="33" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B33" s="48"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
+        <v>71</v>
+      </c>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
     </row>
     <row r="34" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B34" s="48"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
+        <v>72</v>
+      </c>
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
     </row>
     <row r="35" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
+        <v>73</v>
+      </c>
+      <c r="B35" s="27"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
     </row>
     <row r="36" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
+        <v>74</v>
+      </c>
+      <c r="B36" s="27"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
     </row>
     <row r="41" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
+      <c r="A41" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
     </row>
     <row r="42" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="B42" s="39"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="39"/>
+      <c r="A42" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B42" s="31"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
     </row>
     <row r="43" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="B43" s="37"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="37"/>
+      <c r="A43" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
     </row>
     <row r="44" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="B44" s="37"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37"/>
+      <c r="A44" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
     </row>
     <row r="45" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="B45" s="37"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="37"/>
-      <c r="E45" s="37"/>
+      <c r="A45" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
     </row>
     <row r="46" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="B46" s="37"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="37"/>
-      <c r="E46" s="37"/>
+      <c r="A46" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
     </row>
     <row r="47" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="50" t="s">
+      <c r="A47" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B47" s="50"/>
-      <c r="C47" s="50"/>
-      <c r="D47" s="50"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
       <c r="E47" s="8" t="s">
         <v>20</v>
       </c>
@@ -1943,10 +1904,10 @@
       <c r="G47" s="7"/>
     </row>
     <row r="48" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="48"/>
-      <c r="B48" s="48"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
+      <c r="A48" s="27"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="27"/>
       <c r="E48" s="5"/>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
@@ -1961,23 +1922,23 @@
       <c r="G49" s="7"/>
     </row>
     <row r="50" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="B50" s="37"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
+      <c r="A50" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="29"/>
+      <c r="E50" s="29"/>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
     </row>
     <row r="51" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="50" t="s">
+      <c r="A51" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="50"/>
-      <c r="C51" s="50"/>
-      <c r="D51" s="50"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
       <c r="E51" s="8" t="s">
         <v>20</v>
       </c>
@@ -1985,10 +1946,10 @@
       <c r="G51" s="7"/>
     </row>
     <row r="52" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="48"/>
-      <c r="B52" s="48"/>
-      <c r="C52" s="48"/>
-      <c r="D52" s="48"/>
+      <c r="A52" s="27"/>
+      <c r="B52" s="27"/>
+      <c r="C52" s="27"/>
+      <c r="D52" s="27"/>
       <c r="E52" s="5"/>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
@@ -2003,57 +1964,57 @@
       <c r="G53" s="7"/>
     </row>
     <row r="54" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="39"/>
-      <c r="C54" s="39"/>
-      <c r="D54" s="39"/>
-      <c r="E54" s="39"/>
+      <c r="A54" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="31"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="31"/>
+      <c r="E54" s="31"/>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
     </row>
     <row r="55" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="37"/>
-      <c r="C55" s="37"/>
-      <c r="D55" s="37"/>
-      <c r="E55" s="37"/>
+      <c r="A55" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="29"/>
+      <c r="E55" s="29"/>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
     </row>
     <row r="56" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="B56" s="37"/>
-      <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
+      <c r="A56" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="29"/>
       <c r="F56" s="7"/>
       <c r="G56" s="7"/>
     </row>
     <row r="57" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="B57" s="37"/>
-      <c r="C57" s="37"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="37"/>
+      <c r="A57" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
+      <c r="E57" s="29"/>
       <c r="F57" s="7"/>
       <c r="G57" s="7"/>
     </row>
     <row r="58" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="B58" s="37"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
+      <c r="A58" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
       <c r="F58" s="7"/>
       <c r="G58" s="7"/>
     </row>
@@ -2089,7 +2050,7 @@
     </row>
     <row r="61" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -2119,13 +2080,13 @@
       <c r="G63" s="7"/>
     </row>
     <row r="64" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="B64" s="37"/>
-      <c r="C64" s="37"/>
-      <c r="D64" s="37"/>
-      <c r="E64" s="37"/>
+      <c r="A64" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
+      <c r="D64" s="29"/>
+      <c r="E64" s="29"/>
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
     </row>
@@ -2161,7 +2122,7 @@
     </row>
     <row r="67" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -2191,57 +2152,57 @@
       <c r="G69" s="7"/>
     </row>
     <row r="70" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="B70" s="39"/>
-      <c r="C70" s="39"/>
-      <c r="D70" s="39"/>
-      <c r="E70" s="39"/>
+      <c r="A70" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
     </row>
     <row r="71" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="B71" s="37"/>
-      <c r="C71" s="37"/>
-      <c r="D71" s="37"/>
-      <c r="E71" s="37"/>
+      <c r="A71" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B71" s="29"/>
+      <c r="C71" s="29"/>
+      <c r="D71" s="29"/>
+      <c r="E71" s="29"/>
       <c r="F71" s="7"/>
       <c r="G71" s="7"/>
     </row>
     <row r="72" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="B72" s="37"/>
-      <c r="C72" s="37"/>
-      <c r="D72" s="37"/>
-      <c r="E72" s="37"/>
+      <c r="A72" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="B72" s="29"/>
+      <c r="C72" s="29"/>
+      <c r="D72" s="29"/>
+      <c r="E72" s="29"/>
       <c r="F72" s="7"/>
       <c r="G72" s="7"/>
     </row>
     <row r="73" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="B73" s="37"/>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
+      <c r="A73" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="B73" s="29"/>
+      <c r="C73" s="29"/>
+      <c r="D73" s="29"/>
+      <c r="E73" s="29"/>
       <c r="F73" s="7"/>
       <c r="G73" s="7"/>
     </row>
     <row r="74" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="B74" s="37"/>
-      <c r="C74" s="37"/>
-      <c r="D74" s="37"/>
-      <c r="E74" s="37"/>
+      <c r="A74" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="29"/>
+      <c r="C74" s="29"/>
+      <c r="D74" s="29"/>
+      <c r="E74" s="29"/>
       <c r="F74" s="7"/>
       <c r="G74" s="7"/>
     </row>
@@ -2249,10 +2210,10 @@
       <c r="A75" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B75" s="50" t="s">
+      <c r="B75" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="C75" s="50"/>
+      <c r="C75" s="28"/>
       <c r="D75" s="8" t="s">
         <v>20</v>
       </c>
@@ -2261,11 +2222,9 @@
       <c r="G75" s="7"/>
     </row>
     <row r="76" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B76" s="48"/>
-      <c r="C76" s="48"/>
+      <c r="A76" s="5"/>
+      <c r="B76" s="27"/>
+      <c r="C76" s="27"/>
       <c r="D76" s="5"/>
       <c r="E76" s="7"/>
       <c r="F76" s="7"/>
@@ -2281,12 +2240,12 @@
       <c r="G77" s="7"/>
     </row>
     <row r="78" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="37" t="s">
-        <v>82</v>
-      </c>
-      <c r="B78" s="37"/>
-      <c r="C78" s="37"/>
-      <c r="D78" s="37"/>
+      <c r="A78" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="B78" s="29"/>
+      <c r="C78" s="29"/>
+      <c r="D78" s="29"/>
       <c r="E78" s="7"/>
       <c r="F78" s="7"/>
       <c r="G78" s="7"/>
@@ -2295,10 +2254,10 @@
       <c r="A79" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B79" s="50" t="s">
+      <c r="B79" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="C79" s="50"/>
+      <c r="C79" s="28"/>
       <c r="D79" s="8" t="s">
         <v>20</v>
       </c>
@@ -2307,11 +2266,9 @@
       <c r="G79" s="7"/>
     </row>
     <row r="80" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B80" s="48"/>
-      <c r="C80" s="48"/>
+      <c r="A80" s="5"/>
+      <c r="B80" s="27"/>
+      <c r="C80" s="27"/>
       <c r="D80" s="5"/>
       <c r="E80" s="7"/>
       <c r="F80" s="7"/>
@@ -2327,65 +2284,65 @@
       <c r="G81" s="11"/>
     </row>
     <row r="82" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="B82" s="23"/>
-      <c r="C82" s="23"/>
-      <c r="D82" s="23"/>
-      <c r="E82" s="23"/>
+      <c r="A82" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82" s="30"/>
+      <c r="C82" s="30"/>
+      <c r="D82" s="30"/>
+      <c r="E82" s="30"/>
       <c r="F82" s="11"/>
       <c r="G82" s="11"/>
     </row>
     <row r="83" spans="1:7" s="13" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B83" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="C83" s="38"/>
-      <c r="D83" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="B83" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="E83" s="38"/>
-      <c r="F83" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="G83" s="38"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="E83" s="26"/>
+      <c r="F83" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="G83" s="26"/>
     </row>
     <row r="84" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="B84" s="48"/>
-      <c r="C84" s="48"/>
-      <c r="D84" s="48"/>
-      <c r="E84" s="48"/>
-      <c r="F84" s="48"/>
-      <c r="G84" s="48"/>
+        <v>68</v>
+      </c>
+      <c r="B84" s="27"/>
+      <c r="C84" s="27"/>
+      <c r="D84" s="27"/>
+      <c r="E84" s="27"/>
+      <c r="F84" s="27"/>
+      <c r="G84" s="27"/>
     </row>
     <row r="85" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B85" s="48"/>
-      <c r="C85" s="48"/>
-      <c r="D85" s="48"/>
-      <c r="E85" s="48"/>
-      <c r="F85" s="48"/>
-      <c r="G85" s="48"/>
+        <v>69</v>
+      </c>
+      <c r="B85" s="27"/>
+      <c r="C85" s="27"/>
+      <c r="D85" s="27"/>
+      <c r="E85" s="27"/>
+      <c r="F85" s="27"/>
+      <c r="G85" s="27"/>
     </row>
     <row r="86" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B86" s="48"/>
-      <c r="C86" s="48"/>
-      <c r="D86" s="48"/>
-      <c r="E86" s="48"/>
-      <c r="F86" s="48"/>
-      <c r="G86" s="48"/>
+        <v>85</v>
+      </c>
+      <c r="B86" s="27"/>
+      <c r="C86" s="27"/>
+      <c r="D86" s="27"/>
+      <c r="E86" s="27"/>
+      <c r="F86" s="27"/>
+      <c r="G86" s="27"/>
     </row>
     <row r="87" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="11"/>
@@ -2406,35 +2363,35 @@
       <c r="G88" s="11"/>
     </row>
     <row r="89" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="B89" s="23"/>
-      <c r="C89" s="23"/>
-      <c r="D89" s="23"/>
-      <c r="E89" s="23"/>
+      <c r="A89" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B89" s="30"/>
+      <c r="C89" s="30"/>
+      <c r="D89" s="30"/>
+      <c r="E89" s="30"/>
       <c r="F89" s="11"/>
       <c r="G89" s="11"/>
     </row>
     <row r="90" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="B90" s="39"/>
-      <c r="C90" s="39"/>
-      <c r="D90" s="39"/>
-      <c r="E90" s="39"/>
+      <c r="A90" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B90" s="31"/>
+      <c r="C90" s="31"/>
+      <c r="D90" s="31"/>
+      <c r="E90" s="31"/>
       <c r="F90" s="11"/>
       <c r="G90" s="11"/>
     </row>
     <row r="91" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="B91" s="37"/>
-      <c r="C91" s="37"/>
-      <c r="D91" s="37"/>
-      <c r="E91" s="37"/>
+      <c r="A91" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="B91" s="29"/>
+      <c r="C91" s="29"/>
+      <c r="D91" s="29"/>
+      <c r="E91" s="29"/>
       <c r="F91" s="11"/>
       <c r="G91" s="11"/>
     </row>
@@ -2442,300 +2399,312 @@
       <c r="A92" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B92" s="38" t="s">
+      <c r="B92" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C92" s="26"/>
+      <c r="D92" s="26"/>
+      <c r="E92" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="C92" s="38"/>
-      <c r="D92" s="38"/>
-      <c r="E92" s="12" t="s">
+      <c r="F92" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="G92" s="26"/>
+    </row>
+    <row r="93" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A93" s="5"/>
+      <c r="B93" s="43"/>
+      <c r="C93" s="44"/>
+      <c r="D93" s="45"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="43"/>
+      <c r="G93" s="45"/>
+    </row>
+    <row r="94" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A94" s="11"/>
+      <c r="B94" s="11"/>
+      <c r="C94" s="11"/>
+      <c r="D94" s="11"/>
+      <c r="E94" s="11"/>
+      <c r="F94" s="11"/>
+      <c r="G94" s="11"/>
+    </row>
+    <row r="95" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A95" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="F92" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="G92" s="38"/>
-    </row>
-    <row r="93" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="5">
-        <v>1</v>
-      </c>
-      <c r="B93" s="34" t="s">
+      <c r="B95" s="29"/>
+      <c r="C95" s="29"/>
+      <c r="D95" s="29"/>
+      <c r="E95" s="29"/>
+      <c r="F95" s="11"/>
+      <c r="G95" s="11"/>
+    </row>
+    <row r="96" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A96" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C96" s="26"/>
+      <c r="D96" s="26"/>
+      <c r="E96" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="F96" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="G96" s="26"/>
+    </row>
+    <row r="97" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A97" s="5"/>
+      <c r="B97" s="43"/>
+      <c r="C97" s="44"/>
+      <c r="D97" s="45"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="43"/>
+      <c r="G97" s="45"/>
+    </row>
+    <row r="98" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="15"/>
+      <c r="B98" s="15"/>
+      <c r="C98" s="15"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="15"/>
+      <c r="F98" s="15"/>
+      <c r="G98" s="15"/>
+    </row>
+    <row r="99" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A99" s="16"/>
+      <c r="B99" s="16"/>
+      <c r="C99" s="16"/>
+      <c r="D99" s="16"/>
+      <c r="E99" s="16"/>
+      <c r="F99" s="16"/>
+      <c r="G99" s="16"/>
+    </row>
+    <row r="100" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A100" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="C93" s="35"/>
-      <c r="D93" s="36"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="34"/>
-      <c r="G93" s="36"/>
-    </row>
-    <row r="94" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="5">
-        <v>2</v>
-      </c>
-      <c r="B94" s="34" t="s">
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="16"/>
+      <c r="G100" s="16"/>
+    </row>
+    <row r="101" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A101" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="C94" s="35"/>
-      <c r="D94" s="36"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="34"/>
-      <c r="G94" s="36"/>
-    </row>
-    <row r="95" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="5">
-        <v>3</v>
-      </c>
-      <c r="B95" s="34" t="s">
+      <c r="B101" s="31"/>
+      <c r="C101" s="31"/>
+      <c r="D101" s="31"/>
+      <c r="E101" s="31"/>
+      <c r="F101" s="16"/>
+      <c r="G101" s="16"/>
+    </row>
+    <row r="102" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A102" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B102" s="31"/>
+      <c r="C102" s="31"/>
+      <c r="D102" s="31"/>
+      <c r="E102" s="31"/>
+      <c r="F102" s="16"/>
+      <c r="G102" s="16"/>
+    </row>
+    <row r="103" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A103" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="C95" s="35"/>
-      <c r="D95" s="36"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="34"/>
-      <c r="G95" s="36"/>
-    </row>
-    <row r="96" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="5">
-        <v>4</v>
-      </c>
-      <c r="B96" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="C96" s="35"/>
-      <c r="D96" s="36"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="34"/>
-      <c r="G96" s="36"/>
-    </row>
-    <row r="97" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="5">
-        <v>5</v>
-      </c>
-      <c r="B97" s="34" t="s">
+      <c r="B103" s="29"/>
+      <c r="C103" s="29"/>
+      <c r="D103" s="29"/>
+      <c r="E103" s="29"/>
+      <c r="F103" s="16"/>
+      <c r="G103" s="16"/>
+    </row>
+    <row r="104" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A104" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="C97" s="35"/>
-      <c r="D97" s="36"/>
-      <c r="E97" s="5"/>
-      <c r="F97" s="34"/>
-      <c r="G97" s="36"/>
-    </row>
-    <row r="98" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="5">
-        <v>6</v>
-      </c>
-      <c r="B98" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="C98" s="35"/>
-      <c r="D98" s="36"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="34"/>
-      <c r="G98" s="36"/>
-    </row>
-    <row r="99" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="5">
-        <v>7</v>
-      </c>
-      <c r="B99" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="C99" s="35"/>
-      <c r="D99" s="36"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="34"/>
-      <c r="G99" s="36"/>
-    </row>
-    <row r="100" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="11"/>
-      <c r="B100" s="11"/>
-      <c r="C100" s="11"/>
-      <c r="D100" s="11"/>
-      <c r="E100" s="11"/>
-      <c r="F100" s="11"/>
-      <c r="G100" s="11"/>
-    </row>
-    <row r="101" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="B101" s="37"/>
-      <c r="C101" s="37"/>
-      <c r="D101" s="37"/>
-      <c r="E101" s="37"/>
-      <c r="F101" s="11"/>
-      <c r="G101" s="11"/>
-    </row>
-    <row r="102" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B102" s="38" t="s">
+      <c r="C104" s="26"/>
+      <c r="D104" s="26"/>
+      <c r="E104" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="C102" s="38"/>
-      <c r="D102" s="38"/>
-      <c r="E102" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="F102" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="G102" s="38"/>
-    </row>
-    <row r="103" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="5">
-        <v>1</v>
-      </c>
-      <c r="B103" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="C103" s="35"/>
-      <c r="D103" s="36"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="34"/>
-      <c r="G103" s="36"/>
-    </row>
-    <row r="104" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="5">
-        <v>2</v>
-      </c>
-      <c r="B104" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="C104" s="35"/>
-      <c r="D104" s="36"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="34"/>
-      <c r="G104" s="36"/>
+      <c r="F104" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="G104" s="26"/>
     </row>
     <row r="105" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="5">
-        <v>3</v>
-      </c>
-      <c r="B105" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C105" s="35"/>
-      <c r="D105" s="36"/>
+        <v>1</v>
+      </c>
+      <c r="B105" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C105" s="44"/>
+      <c r="D105" s="45"/>
       <c r="E105" s="5"/>
-      <c r="F105" s="34"/>
-      <c r="G105" s="36"/>
+      <c r="F105" s="43"/>
+      <c r="G105" s="45"/>
     </row>
     <row r="106" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="5">
-        <v>4</v>
-      </c>
-      <c r="B106" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="C106" s="35"/>
-      <c r="D106" s="36"/>
+        <v>2</v>
+      </c>
+      <c r="B106" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="C106" s="44"/>
+      <c r="D106" s="45"/>
       <c r="E106" s="5"/>
-      <c r="F106" s="34"/>
-      <c r="G106" s="36"/>
+      <c r="F106" s="43"/>
+      <c r="G106" s="45"/>
     </row>
     <row r="107" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="5">
-        <v>5</v>
-      </c>
-      <c r="B107" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="C107" s="35"/>
-      <c r="D107" s="36"/>
+        <v>3</v>
+      </c>
+      <c r="B107" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="C107" s="44"/>
+      <c r="D107" s="45"/>
       <c r="E107" s="5"/>
-      <c r="F107" s="34"/>
-      <c r="G107" s="36"/>
+      <c r="F107" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="G107" s="45"/>
     </row>
     <row r="108" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="5">
-        <v>6</v>
-      </c>
-      <c r="B108" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="C108" s="35"/>
-      <c r="D108" s="36"/>
+        <v>4</v>
+      </c>
+      <c r="B108" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C108" s="44"/>
+      <c r="D108" s="45"/>
       <c r="E108" s="5"/>
-      <c r="F108" s="34"/>
-      <c r="G108" s="36"/>
+      <c r="F108" s="43"/>
+      <c r="G108" s="45"/>
     </row>
     <row r="109" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="5">
+        <v>5</v>
+      </c>
+      <c r="B109" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="C109" s="44"/>
+      <c r="D109" s="45"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="G109" s="45"/>
+    </row>
+    <row r="110" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A110" s="5">
+        <v>6</v>
+      </c>
+      <c r="B110" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="C110" s="44"/>
+      <c r="D110" s="45"/>
+      <c r="E110" s="5"/>
+      <c r="F110" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="G110" s="45"/>
+    </row>
+    <row r="111" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A111" s="5">
         <v>7</v>
       </c>
-      <c r="B109" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="C109" s="35"/>
-      <c r="D109" s="36"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="34"/>
-      <c r="G109" s="36"/>
-    </row>
-    <row r="110" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="15"/>
-      <c r="B110" s="15"/>
-      <c r="C110" s="15"/>
-      <c r="D110" s="15"/>
-      <c r="E110" s="15"/>
-      <c r="F110" s="15"/>
-      <c r="G110" s="15"/>
-    </row>
-    <row r="111" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="16"/>
-      <c r="B111" s="16"/>
-      <c r="C111" s="16"/>
-      <c r="D111" s="16"/>
-      <c r="E111" s="16"/>
-      <c r="F111" s="16"/>
-      <c r="G111" s="16"/>
+      <c r="B111" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="C111" s="44"/>
+      <c r="D111" s="45"/>
+      <c r="E111" s="5"/>
+      <c r="F111" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="G111" s="45"/>
     </row>
     <row r="112" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="16"/>
-      <c r="B112" s="16"/>
-      <c r="C112" s="16"/>
-      <c r="D112" s="16"/>
-      <c r="E112" s="16"/>
-      <c r="F112" s="16"/>
-      <c r="G112" s="16"/>
+      <c r="A112" s="5">
+        <v>8</v>
+      </c>
+      <c r="B112" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="C112" s="44"/>
+      <c r="D112" s="45"/>
+      <c r="E112" s="5"/>
+      <c r="F112" s="43"/>
+      <c r="G112" s="45"/>
     </row>
     <row r="113" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="16"/>
-      <c r="B113" s="16"/>
-      <c r="C113" s="16"/>
-      <c r="D113" s="16"/>
-      <c r="E113" s="16"/>
-      <c r="F113" s="16"/>
-      <c r="G113" s="16"/>
+      <c r="A113" s="5">
+        <v>9</v>
+      </c>
+      <c r="B113" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="C113" s="44"/>
+      <c r="D113" s="45"/>
+      <c r="E113" s="5"/>
+      <c r="F113" s="43"/>
+      <c r="G113" s="45"/>
     </row>
     <row r="114" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="16"/>
-      <c r="B114" s="16"/>
-      <c r="C114" s="16"/>
-      <c r="D114" s="16"/>
-      <c r="E114" s="16"/>
-      <c r="F114" s="16"/>
-      <c r="G114" s="16"/>
+      <c r="A114" s="5">
+        <v>10</v>
+      </c>
+      <c r="B114" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="C114" s="44"/>
+      <c r="D114" s="45"/>
+      <c r="E114" s="5"/>
+      <c r="F114" s="43"/>
+      <c r="G114" s="45"/>
     </row>
     <row r="115" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="16"/>
-      <c r="B115" s="16"/>
-      <c r="C115" s="16"/>
-      <c r="D115" s="16"/>
-      <c r="E115" s="16"/>
-      <c r="F115" s="16"/>
-      <c r="G115" s="16"/>
+      <c r="A115" s="5">
+        <v>11</v>
+      </c>
+      <c r="B115" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="C115" s="44"/>
+      <c r="D115" s="45"/>
+      <c r="E115" s="5"/>
+      <c r="F115" s="43"/>
+      <c r="G115" s="45"/>
     </row>
     <row r="116" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="16"/>
-      <c r="B116" s="16"/>
-      <c r="C116" s="16"/>
-      <c r="D116" s="16"/>
-      <c r="E116" s="16"/>
-      <c r="F116" s="16"/>
-      <c r="G116" s="16"/>
+      <c r="A116" s="6"/>
+      <c r="B116" s="17"/>
+      <c r="C116" s="17"/>
+      <c r="D116" s="17"/>
+      <c r="E116" s="6"/>
+      <c r="F116" s="17"/>
+      <c r="G116" s="17"/>
     </row>
     <row r="117" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="16"/>
@@ -2747,31 +2716,45 @@
       <c r="G117" s="16"/>
     </row>
     <row r="118" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="16"/>
-      <c r="B118" s="16"/>
-      <c r="C118" s="16"/>
-      <c r="D118" s="16"/>
-      <c r="E118" s="16"/>
+      <c r="A118" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="B118" s="30"/>
+      <c r="C118" s="30"/>
+      <c r="D118" s="30"/>
+      <c r="E118" s="30"/>
       <c r="F118" s="16"/>
       <c r="G118" s="16"/>
     </row>
     <row r="119" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="16"/>
-      <c r="B119" s="16"/>
-      <c r="C119" s="16"/>
-      <c r="D119" s="16"/>
-      <c r="E119" s="16"/>
-      <c r="F119" s="16"/>
-      <c r="G119" s="16"/>
+      <c r="A119" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="B119" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C119" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D119" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E119" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="F119" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="G119" s="23"/>
     </row>
     <row r="120" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="16"/>
-      <c r="B120" s="16"/>
-      <c r="C120" s="16"/>
-      <c r="D120" s="16"/>
-      <c r="E120" s="16"/>
-      <c r="F120" s="16"/>
-      <c r="G120" s="16"/>
+      <c r="A120" s="21"/>
+      <c r="B120" s="21"/>
+      <c r="C120" s="21"/>
+      <c r="D120" s="21"/>
+      <c r="E120" s="21"/>
+      <c r="F120" s="46"/>
+      <c r="G120" s="46"/>
     </row>
     <row r="121" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="16"/>
@@ -2783,225 +2766,189 @@
       <c r="G121" s="16"/>
     </row>
     <row r="122" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="B122" s="23"/>
-      <c r="C122" s="23"/>
-      <c r="D122" s="23"/>
-      <c r="E122" s="23"/>
+      <c r="A122" s="16"/>
+      <c r="B122" s="16"/>
+      <c r="C122" s="16"/>
+      <c r="D122" s="16"/>
+      <c r="E122" s="16"/>
       <c r="F122" s="16"/>
       <c r="G122" s="16"/>
     </row>
     <row r="123" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="B123" s="39"/>
-      <c r="C123" s="39"/>
-      <c r="D123" s="39"/>
-      <c r="E123" s="39"/>
+      <c r="A123" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B123" s="30"/>
+      <c r="C123" s="30"/>
+      <c r="D123" s="30"/>
+      <c r="E123" s="30"/>
       <c r="F123" s="16"/>
       <c r="G123" s="16"/>
     </row>
     <row r="124" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="B124" s="39"/>
-      <c r="C124" s="39"/>
-      <c r="D124" s="39"/>
-      <c r="E124" s="39"/>
-      <c r="F124" s="16"/>
+      <c r="A124" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B124" s="23"/>
+      <c r="C124" s="23"/>
+      <c r="D124" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="E124" s="23"/>
+      <c r="F124" s="23"/>
       <c r="G124" s="16"/>
     </row>
     <row r="125" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="37" t="s">
-        <v>101</v>
-      </c>
-      <c r="B125" s="37"/>
-      <c r="C125" s="37"/>
-      <c r="D125" s="37"/>
-      <c r="E125" s="37"/>
-      <c r="F125" s="16"/>
+      <c r="A125" s="46"/>
+      <c r="B125" s="46"/>
+      <c r="C125" s="46"/>
+      <c r="D125" s="46"/>
+      <c r="E125" s="46"/>
+      <c r="F125" s="46"/>
       <c r="G125" s="16"/>
     </row>
     <row r="126" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B126" s="38" t="s">
-        <v>103</v>
-      </c>
-      <c r="C126" s="38"/>
-      <c r="D126" s="38"/>
-      <c r="E126" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="F126" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="G126" s="38"/>
+      <c r="A126" s="16"/>
+      <c r="B126" s="16"/>
+      <c r="C126" s="16"/>
+      <c r="D126" s="16"/>
+      <c r="E126" s="16"/>
+      <c r="F126" s="16"/>
+      <c r="G126" s="16"/>
     </row>
     <row r="127" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="5">
-        <v>1</v>
-      </c>
-      <c r="B127" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="C127" s="35"/>
-      <c r="D127" s="36"/>
-      <c r="E127" s="5"/>
-      <c r="F127" s="34"/>
-      <c r="G127" s="36"/>
+      <c r="A127" s="16"/>
+      <c r="B127" s="16"/>
+      <c r="C127" s="16"/>
+      <c r="D127" s="16"/>
+      <c r="E127" s="16"/>
+      <c r="F127" s="16"/>
+      <c r="G127" s="16"/>
     </row>
     <row r="128" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="5">
-        <v>2</v>
-      </c>
-      <c r="B128" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="C128" s="35"/>
-      <c r="D128" s="36"/>
-      <c r="E128" s="5"/>
-      <c r="F128" s="34"/>
-      <c r="G128" s="36"/>
+      <c r="A128" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="B128" s="30"/>
+      <c r="C128" s="30"/>
+      <c r="D128" s="30"/>
+      <c r="E128" s="30"/>
+      <c r="F128" s="16"/>
+      <c r="G128" s="16"/>
     </row>
     <row r="129" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="5">
-        <v>3</v>
-      </c>
-      <c r="B129" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="C129" s="35"/>
-      <c r="D129" s="36"/>
-      <c r="E129" s="5"/>
-      <c r="F129" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="G129" s="36"/>
+      <c r="A129" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B129" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C129" s="23"/>
+      <c r="D129" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="E129" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="F129" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="G129" s="23"/>
     </row>
     <row r="130" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="5">
-        <v>4</v>
-      </c>
-      <c r="B130" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="C130" s="35"/>
-      <c r="D130" s="36"/>
-      <c r="E130" s="5"/>
-      <c r="F130" s="34"/>
-      <c r="G130" s="36"/>
+      <c r="A130" s="19"/>
+      <c r="B130" s="24"/>
+      <c r="C130" s="25"/>
+      <c r="D130" s="19"/>
+      <c r="E130" s="19"/>
+      <c r="F130" s="24"/>
+      <c r="G130" s="25"/>
     </row>
     <row r="131" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="5">
-        <v>5</v>
-      </c>
-      <c r="B131" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="C131" s="35"/>
-      <c r="D131" s="36"/>
-      <c r="E131" s="5"/>
-      <c r="F131" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="G131" s="36"/>
+      <c r="A131" s="16"/>
+      <c r="B131" s="16"/>
+      <c r="C131" s="16"/>
+      <c r="D131" s="16"/>
+      <c r="E131" s="16"/>
+      <c r="F131" s="16"/>
+      <c r="G131" s="16"/>
     </row>
     <row r="132" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="5">
-        <v>6</v>
-      </c>
-      <c r="B132" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="C132" s="35"/>
-      <c r="D132" s="36"/>
-      <c r="E132" s="5"/>
-      <c r="F132" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="G132" s="36"/>
+      <c r="A132" s="16"/>
+      <c r="B132" s="16"/>
+      <c r="C132" s="16"/>
+      <c r="D132" s="16"/>
+      <c r="E132" s="16"/>
+      <c r="F132" s="16"/>
+      <c r="G132" s="16"/>
     </row>
     <row r="133" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="5">
-        <v>7</v>
-      </c>
-      <c r="B133" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="C133" s="35"/>
-      <c r="D133" s="36"/>
-      <c r="E133" s="5"/>
-      <c r="F133" s="34" t="s">
-        <v>117</v>
-      </c>
-      <c r="G133" s="36"/>
+      <c r="A133" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="B133" s="30"/>
+      <c r="C133" s="30"/>
+      <c r="D133" s="30"/>
+      <c r="E133" s="30"/>
+      <c r="F133" s="16"/>
+      <c r="G133" s="16"/>
     </row>
     <row r="134" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="5">
-        <v>8</v>
-      </c>
-      <c r="B134" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="C134" s="35"/>
-      <c r="D134" s="36"/>
-      <c r="E134" s="5"/>
-      <c r="F134" s="34"/>
-      <c r="G134" s="36"/>
+      <c r="A134" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="B134" s="23"/>
+      <c r="C134" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="D134" s="23"/>
+      <c r="E134" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="F134" s="23"/>
+      <c r="G134" s="16"/>
     </row>
     <row r="135" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="5">
-        <v>9</v>
-      </c>
-      <c r="B135" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="C135" s="35"/>
-      <c r="D135" s="36"/>
-      <c r="E135" s="5"/>
-      <c r="F135" s="34"/>
-      <c r="G135" s="36"/>
+      <c r="A135" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B135" s="25"/>
+      <c r="C135" s="24"/>
+      <c r="D135" s="25"/>
+      <c r="E135" s="24"/>
+      <c r="F135" s="25"/>
+      <c r="G135" s="16"/>
     </row>
     <row r="136" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="5">
-        <v>10</v>
-      </c>
-      <c r="B136" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="C136" s="35"/>
-      <c r="D136" s="36"/>
-      <c r="E136" s="5"/>
-      <c r="F136" s="34"/>
-      <c r="G136" s="36"/>
+      <c r="A136" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B136" s="25"/>
+      <c r="C136" s="24"/>
+      <c r="D136" s="25"/>
+      <c r="E136" s="24"/>
+      <c r="F136" s="25"/>
+      <c r="G136" s="16"/>
     </row>
     <row r="137" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="5">
-        <v>11</v>
-      </c>
-      <c r="B137" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="C137" s="35"/>
-      <c r="D137" s="36"/>
-      <c r="E137" s="5"/>
-      <c r="F137" s="34"/>
-      <c r="G137" s="36"/>
+      <c r="A137" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B137" s="25"/>
+      <c r="C137" s="24"/>
+      <c r="D137" s="25"/>
+      <c r="E137" s="24"/>
+      <c r="F137" s="25"/>
+      <c r="G137" s="16"/>
     </row>
     <row r="138" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="6"/>
-      <c r="B138" s="17"/>
-      <c r="C138" s="17"/>
-      <c r="D138" s="17"/>
-      <c r="E138" s="6"/>
-      <c r="F138" s="17"/>
-      <c r="G138" s="17"/>
+      <c r="A138" s="16"/>
+      <c r="B138" s="16"/>
+      <c r="C138" s="16"/>
+      <c r="D138" s="16"/>
+      <c r="E138" s="16"/>
+      <c r="F138" s="16"/>
+      <c r="G138" s="16"/>
     </row>
     <row r="139" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="16"/>
@@ -3013,699 +2960,176 @@
       <c r="G139" s="16"/>
     </row>
     <row r="140" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="B140" s="23"/>
-      <c r="C140" s="23"/>
-      <c r="D140" s="23"/>
-      <c r="E140" s="23"/>
+      <c r="A140" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="B140" s="30"/>
+      <c r="C140" s="30"/>
+      <c r="D140" s="30"/>
+      <c r="E140" s="30"/>
       <c r="F140" s="16"/>
       <c r="G140" s="16"/>
     </row>
     <row r="141" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="B141" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="C141" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D141" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="E141" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="F141" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="G141" s="24"/>
+      <c r="A141" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B141" s="23"/>
+      <c r="C141" s="23"/>
+      <c r="D141" s="23"/>
+      <c r="E141" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="F141" s="23"/>
+      <c r="G141" s="23"/>
     </row>
     <row r="142" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="B142" s="21"/>
-      <c r="C142" s="21"/>
-      <c r="D142" s="21"/>
-      <c r="E142" s="21"/>
-      <c r="F142" s="51"/>
-      <c r="G142" s="51"/>
+      <c r="A142" s="47"/>
+      <c r="B142" s="48"/>
+      <c r="C142" s="48"/>
+      <c r="D142" s="49"/>
+      <c r="E142" s="47"/>
+      <c r="F142" s="48"/>
+      <c r="G142" s="49"/>
     </row>
     <row r="143" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="16"/>
-      <c r="B143" s="16"/>
-      <c r="C143" s="16"/>
-      <c r="D143" s="16"/>
-      <c r="E143" s="16"/>
-      <c r="F143" s="16"/>
-      <c r="G143" s="16"/>
-    </row>
-    <row r="144" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="16"/>
-      <c r="B144" s="16"/>
-      <c r="C144" s="16"/>
-      <c r="D144" s="16"/>
-      <c r="E144" s="16"/>
-      <c r="F144" s="16"/>
-      <c r="G144" s="16"/>
+      <c r="A143" s="20"/>
+      <c r="B143" s="20"/>
+      <c r="C143" s="20"/>
+      <c r="D143" s="20"/>
+      <c r="E143" s="20"/>
+      <c r="F143" s="20"/>
+      <c r="G143" s="20"/>
     </row>
     <row r="145" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="16"/>
-      <c r="B145" s="16"/>
-      <c r="C145" s="16"/>
-      <c r="D145" s="16"/>
-      <c r="E145" s="16"/>
-      <c r="F145" s="16"/>
-      <c r="G145" s="16"/>
+      <c r="A145" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="B145" s="30"/>
+      <c r="C145" s="30"/>
+      <c r="D145" s="30"/>
+      <c r="E145" s="30"/>
     </row>
     <row r="146" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="16"/>
-      <c r="B146" s="16"/>
-      <c r="C146" s="16"/>
-      <c r="D146" s="16"/>
-      <c r="E146" s="16"/>
-      <c r="F146" s="16"/>
-      <c r="G146" s="16"/>
+      <c r="A146" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B146" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="C146" s="33"/>
+      <c r="D146" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="E146" s="33"/>
+      <c r="F146" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="147" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="16"/>
-      <c r="B147" s="16"/>
-      <c r="C147" s="16"/>
-      <c r="D147" s="16"/>
-      <c r="E147" s="16"/>
-      <c r="F147" s="16"/>
-      <c r="G147" s="16"/>
-    </row>
-    <row r="148" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="16"/>
-      <c r="B148" s="16"/>
-      <c r="C148" s="16"/>
-      <c r="D148" s="16"/>
-      <c r="E148" s="16"/>
-      <c r="F148" s="16"/>
-      <c r="G148" s="16"/>
-    </row>
-    <row r="149" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="16"/>
-      <c r="B149" s="16"/>
-      <c r="C149" s="16"/>
-      <c r="D149" s="16"/>
-      <c r="E149" s="16"/>
-      <c r="F149" s="16"/>
-      <c r="G149" s="16"/>
-    </row>
-    <row r="150" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="16"/>
-      <c r="B150" s="16"/>
-      <c r="C150" s="16"/>
-      <c r="D150" s="16"/>
-      <c r="E150" s="16"/>
-      <c r="F150" s="16"/>
-      <c r="G150" s="16"/>
-    </row>
-    <row r="151" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="16"/>
-      <c r="B151" s="16"/>
-      <c r="C151" s="16"/>
-      <c r="D151" s="16"/>
-      <c r="E151" s="16"/>
-      <c r="F151" s="16"/>
-      <c r="G151" s="16"/>
-    </row>
-    <row r="152" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="16"/>
-      <c r="B152" s="16"/>
-      <c r="C152" s="16"/>
-      <c r="D152" s="16"/>
-      <c r="E152" s="16"/>
-      <c r="F152" s="16"/>
-      <c r="G152" s="16"/>
-    </row>
-    <row r="153" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="16"/>
-      <c r="B153" s="16"/>
-      <c r="C153" s="16"/>
-      <c r="D153" s="16"/>
-      <c r="E153" s="16"/>
-      <c r="F153" s="16"/>
-      <c r="G153" s="16"/>
-    </row>
-    <row r="154" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="16"/>
-      <c r="B154" s="16"/>
-      <c r="C154" s="16"/>
-      <c r="D154" s="16"/>
-      <c r="E154" s="16"/>
-      <c r="F154" s="16"/>
-      <c r="G154" s="16"/>
-    </row>
-    <row r="155" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="16"/>
-      <c r="B155" s="16"/>
-      <c r="C155" s="16"/>
-      <c r="D155" s="16"/>
-      <c r="E155" s="16"/>
-      <c r="F155" s="16"/>
-      <c r="G155" s="16"/>
-    </row>
-    <row r="156" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="16"/>
-      <c r="B156" s="16"/>
-      <c r="C156" s="16"/>
-      <c r="D156" s="16"/>
-      <c r="E156" s="16"/>
-      <c r="F156" s="16"/>
-      <c r="G156" s="16"/>
-    </row>
-    <row r="157" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="16"/>
-      <c r="B157" s="16"/>
-      <c r="C157" s="16"/>
-      <c r="D157" s="16"/>
-      <c r="E157" s="16"/>
-      <c r="F157" s="16"/>
-      <c r="G157" s="16"/>
-    </row>
-    <row r="158" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="16"/>
-      <c r="B158" s="16"/>
-      <c r="C158" s="16"/>
-      <c r="D158" s="16"/>
-      <c r="E158" s="16"/>
-      <c r="F158" s="16"/>
-      <c r="G158" s="16"/>
-    </row>
-    <row r="159" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="16"/>
-      <c r="B159" s="16"/>
-      <c r="C159" s="16"/>
-      <c r="D159" s="16"/>
-      <c r="E159" s="16"/>
-      <c r="F159" s="16"/>
-      <c r="G159" s="16"/>
-    </row>
-    <row r="160" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="16"/>
-      <c r="B160" s="16"/>
-      <c r="C160" s="16"/>
-      <c r="D160" s="16"/>
-      <c r="E160" s="16"/>
-      <c r="F160" s="16"/>
-      <c r="G160" s="16"/>
-    </row>
-    <row r="161" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="16"/>
-      <c r="B161" s="16"/>
-      <c r="C161" s="16"/>
-      <c r="D161" s="16"/>
-      <c r="E161" s="16"/>
-      <c r="F161" s="16"/>
-      <c r="G161" s="16"/>
-    </row>
-    <row r="162" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="B162" s="23"/>
-      <c r="C162" s="23"/>
-      <c r="D162" s="23"/>
-      <c r="E162" s="23"/>
-      <c r="F162" s="16"/>
-      <c r="G162" s="16"/>
-    </row>
-    <row r="163" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="B163" s="24"/>
-      <c r="C163" s="24"/>
-      <c r="D163" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="E163" s="24"/>
-      <c r="F163" s="24"/>
-      <c r="G163" s="16"/>
-    </row>
-    <row r="164" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A164" s="51"/>
-      <c r="B164" s="51"/>
-      <c r="C164" s="51"/>
-      <c r="D164" s="51"/>
-      <c r="E164" s="51"/>
-      <c r="F164" s="51"/>
-      <c r="G164" s="16"/>
-    </row>
-    <row r="165" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="16"/>
-      <c r="B165" s="16"/>
-      <c r="C165" s="16"/>
-      <c r="D165" s="16"/>
-      <c r="E165" s="16"/>
-      <c r="F165" s="16"/>
-      <c r="G165" s="16"/>
-    </row>
-    <row r="166" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A166" s="16"/>
-      <c r="B166" s="16"/>
-      <c r="C166" s="16"/>
-      <c r="D166" s="16"/>
-      <c r="E166" s="16"/>
-      <c r="F166" s="16"/>
-      <c r="G166" s="16"/>
-    </row>
-    <row r="167" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A167" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="B167" s="23"/>
-      <c r="C167" s="23"/>
-      <c r="D167" s="23"/>
-      <c r="E167" s="23"/>
-      <c r="F167" s="16"/>
-      <c r="G167" s="16"/>
-    </row>
-    <row r="168" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="B168" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="C168" s="24"/>
-      <c r="D168" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="E168" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="F168" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="G168" s="24"/>
-    </row>
-    <row r="169" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A169" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="B169" s="32"/>
-      <c r="C169" s="33"/>
-      <c r="D169" s="19"/>
-      <c r="E169" s="19"/>
-      <c r="F169" s="32"/>
-      <c r="G169" s="33"/>
-    </row>
-    <row r="170" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A170" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="B170" s="32"/>
-      <c r="C170" s="33"/>
-      <c r="D170" s="19"/>
-      <c r="E170" s="19"/>
-      <c r="F170" s="32"/>
-      <c r="G170" s="33"/>
-    </row>
-    <row r="171" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A171" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="B171" s="32"/>
-      <c r="C171" s="33"/>
-      <c r="D171" s="19"/>
-      <c r="E171" s="19"/>
-      <c r="F171" s="32"/>
-      <c r="G171" s="33"/>
-    </row>
-    <row r="172" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A172" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="B172" s="32"/>
-      <c r="C172" s="33"/>
-      <c r="D172" s="19"/>
-      <c r="E172" s="19"/>
-      <c r="F172" s="32"/>
-      <c r="G172" s="33"/>
-    </row>
-    <row r="173" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A173" s="16"/>
-      <c r="B173" s="16"/>
-      <c r="C173" s="16"/>
-      <c r="D173" s="16"/>
-      <c r="E173" s="16"/>
-      <c r="F173" s="16"/>
-      <c r="G173" s="16"/>
-    </row>
-    <row r="174" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A174" s="16"/>
-      <c r="B174" s="16"/>
-      <c r="C174" s="16"/>
-      <c r="D174" s="16"/>
-      <c r="E174" s="16"/>
-      <c r="F174" s="16"/>
-      <c r="G174" s="16"/>
-    </row>
-    <row r="175" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A175" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="B175" s="23"/>
-      <c r="C175" s="23"/>
-      <c r="D175" s="23"/>
-      <c r="E175" s="23"/>
-      <c r="F175" s="16"/>
-      <c r="G175" s="16"/>
-    </row>
-    <row r="176" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="B176" s="24"/>
-      <c r="C176" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="D176" s="24"/>
-      <c r="E176" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="F176" s="24"/>
-      <c r="G176" s="16"/>
-    </row>
-    <row r="177" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A177" s="32" t="s">
-        <v>139</v>
-      </c>
-      <c r="B177" s="33"/>
-      <c r="C177" s="32"/>
-      <c r="D177" s="33"/>
-      <c r="E177" s="32"/>
-      <c r="F177" s="33"/>
-      <c r="G177" s="16"/>
-    </row>
-    <row r="178" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A178" s="32" t="s">
-        <v>140</v>
-      </c>
-      <c r="B178" s="33"/>
-      <c r="C178" s="32"/>
-      <c r="D178" s="33"/>
-      <c r="E178" s="32"/>
-      <c r="F178" s="33"/>
-      <c r="G178" s="16"/>
-    </row>
-    <row r="179" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A179" s="32" t="s">
-        <v>141</v>
-      </c>
-      <c r="B179" s="33"/>
-      <c r="C179" s="32"/>
-      <c r="D179" s="33"/>
-      <c r="E179" s="32"/>
-      <c r="F179" s="33"/>
-      <c r="G179" s="16"/>
-    </row>
-    <row r="180" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A180" s="16"/>
-      <c r="B180" s="16"/>
-      <c r="C180" s="16"/>
-      <c r="D180" s="16"/>
-      <c r="E180" s="16"/>
-      <c r="F180" s="16"/>
-      <c r="G180" s="16"/>
-    </row>
-    <row r="181" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A181" s="16"/>
-      <c r="B181" s="16"/>
-      <c r="C181" s="16"/>
-      <c r="D181" s="16"/>
-      <c r="E181" s="16"/>
-      <c r="F181" s="16"/>
-      <c r="G181" s="16"/>
-    </row>
-    <row r="182" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A182" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="B182" s="23"/>
-      <c r="C182" s="23"/>
-      <c r="D182" s="23"/>
-      <c r="E182" s="23"/>
-      <c r="F182" s="16"/>
-      <c r="G182" s="16"/>
-    </row>
-    <row r="183" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="B183" s="24"/>
-      <c r="C183" s="24"/>
-      <c r="D183" s="24"/>
-      <c r="E183" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="F183" s="24"/>
-      <c r="G183" s="24"/>
-    </row>
-    <row r="184" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="27"/>
-      <c r="B184" s="28"/>
-      <c r="C184" s="28"/>
-      <c r="D184" s="29"/>
-      <c r="E184" s="27"/>
-      <c r="F184" s="28"/>
-      <c r="G184" s="29"/>
-    </row>
-    <row r="185" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A185" s="20"/>
-      <c r="B185" s="20"/>
-      <c r="C185" s="20"/>
-      <c r="D185" s="20"/>
-      <c r="E185" s="20"/>
-      <c r="F185" s="20"/>
-      <c r="G185" s="20"/>
-    </row>
-    <row r="186" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A186" s="20"/>
-      <c r="B186" s="20"/>
-      <c r="C186" s="20"/>
-      <c r="D186" s="20"/>
-      <c r="E186" s="20"/>
-      <c r="F186" s="20"/>
-      <c r="G186" s="20"/>
-    </row>
-    <row r="187" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A187" s="20"/>
-      <c r="B187" s="20"/>
-      <c r="C187" s="20"/>
-      <c r="D187" s="20"/>
-      <c r="E187" s="20"/>
-      <c r="F187" s="20"/>
-      <c r="G187" s="20"/>
-    </row>
-    <row r="188" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A188" s="20"/>
-      <c r="B188" s="20"/>
-      <c r="C188" s="20"/>
-      <c r="D188" s="20"/>
-      <c r="E188" s="20"/>
-      <c r="F188" s="20"/>
-      <c r="G188" s="20"/>
-    </row>
-    <row r="189" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A189" s="20"/>
-      <c r="B189" s="20"/>
-      <c r="C189" s="20"/>
-      <c r="D189" s="20"/>
-      <c r="E189" s="20"/>
-      <c r="F189" s="20"/>
-      <c r="G189" s="20"/>
-    </row>
-    <row r="190" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A190" s="20"/>
-      <c r="B190" s="20"/>
-      <c r="C190" s="20"/>
-      <c r="D190" s="20"/>
-      <c r="E190" s="20"/>
-      <c r="F190" s="20"/>
-      <c r="G190" s="20"/>
-    </row>
-    <row r="191" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A191" s="20"/>
-      <c r="B191" s="20"/>
-      <c r="C191" s="20"/>
-      <c r="D191" s="20"/>
-      <c r="E191" s="20"/>
-      <c r="F191" s="20"/>
-      <c r="G191" s="20"/>
-    </row>
-    <row r="192" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A192" s="20"/>
-      <c r="B192" s="20"/>
-      <c r="C192" s="20"/>
-      <c r="D192" s="20"/>
-      <c r="E192" s="20"/>
-      <c r="F192" s="20"/>
-      <c r="G192" s="20"/>
-    </row>
-    <row r="193" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A193" s="20"/>
-      <c r="B193" s="20"/>
-      <c r="C193" s="20"/>
-      <c r="D193" s="20"/>
-      <c r="E193" s="20"/>
-      <c r="F193" s="20"/>
-      <c r="G193" s="20"/>
-    </row>
-    <row r="194" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A194" s="16"/>
-      <c r="B194" s="16"/>
-      <c r="C194" s="16"/>
-      <c r="D194" s="16"/>
-      <c r="E194" s="16"/>
-      <c r="F194" s="16"/>
-      <c r="G194" s="16"/>
-    </row>
-    <row r="195" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A195" s="16"/>
-      <c r="B195" s="16"/>
-      <c r="C195" s="16"/>
-      <c r="D195" s="16"/>
-      <c r="E195" s="16"/>
-      <c r="F195" s="16"/>
-      <c r="G195" s="16"/>
-    </row>
-    <row r="196" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A196" s="16"/>
-      <c r="B196" s="16"/>
-      <c r="C196" s="16"/>
-      <c r="D196" s="16"/>
-      <c r="E196" s="16"/>
-      <c r="F196" s="16"/>
-      <c r="G196" s="16"/>
-    </row>
-    <row r="197" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="16"/>
-      <c r="B197" s="16"/>
-      <c r="C197" s="16"/>
-      <c r="D197" s="16"/>
-      <c r="E197" s="16"/>
-      <c r="F197" s="16"/>
-      <c r="G197" s="16"/>
-    </row>
-    <row r="198" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="16"/>
-      <c r="B198" s="16"/>
-      <c r="C198" s="16"/>
-      <c r="D198" s="16"/>
-      <c r="E198" s="16"/>
-      <c r="F198" s="16"/>
-      <c r="G198" s="16"/>
-    </row>
-    <row r="199" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="16"/>
-      <c r="B199" s="16"/>
-      <c r="C199" s="16"/>
-      <c r="D199" s="16"/>
-      <c r="E199" s="16"/>
-      <c r="F199" s="16"/>
-      <c r="G199" s="16"/>
-    </row>
-    <row r="201" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="B201" s="23"/>
-      <c r="C201" s="23"/>
-      <c r="D201" s="23"/>
-      <c r="E201" s="23"/>
-    </row>
-    <row r="202" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B202" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="C202" s="25"/>
-      <c r="D202" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="E202" s="25"/>
-      <c r="F202" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G202" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A203" s="3"/>
-      <c r="B203" s="30"/>
-      <c r="C203" s="31"/>
-      <c r="D203" s="26"/>
-      <c r="E203" s="26"/>
-      <c r="F203" s="3"/>
-      <c r="G203" s="3"/>
+      <c r="A147" s="3"/>
+      <c r="B147" s="50"/>
+      <c r="C147" s="51"/>
+      <c r="D147" s="32"/>
+      <c r="E147" s="32"/>
+      <c r="F147" s="3"/>
+      <c r="G147" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="199">
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="E176:F176"/>
-    <mergeCell ref="A177:B177"/>
-    <mergeCell ref="A178:B178"/>
-    <mergeCell ref="F168:G168"/>
-    <mergeCell ref="F169:G169"/>
-    <mergeCell ref="F170:G170"/>
-    <mergeCell ref="F171:G171"/>
-    <mergeCell ref="F83:G83"/>
-    <mergeCell ref="D83:E83"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="D84:E84"/>
-    <mergeCell ref="D85:E85"/>
-    <mergeCell ref="D86:E86"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="A78:D78"/>
-    <mergeCell ref="A82:E82"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A73:E73"/>
-    <mergeCell ref="A74:E74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
+  <mergeCells count="169">
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A141:D141"/>
+    <mergeCell ref="E141:G141"/>
+    <mergeCell ref="A145:E145"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="D146:E146"/>
+    <mergeCell ref="D147:E147"/>
+    <mergeCell ref="A142:D142"/>
+    <mergeCell ref="E142:G142"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="F119:G119"/>
+    <mergeCell ref="F120:G120"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="E136:F136"/>
+    <mergeCell ref="E137:F137"/>
+    <mergeCell ref="A137:B137"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="D125:F125"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="A133:E133"/>
+    <mergeCell ref="A134:B134"/>
+    <mergeCell ref="B111:D111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="F112:G112"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="F113:G113"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="F114:G114"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="F115:G115"/>
+    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="F108:G108"/>
+    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="F109:G109"/>
+    <mergeCell ref="B110:D110"/>
+    <mergeCell ref="F110:G110"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="B105:D105"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="F107:G107"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A7:A16"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:F19"/>
+    <mergeCell ref="C7:F7"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="C6:G6"/>
@@ -3730,128 +3154,61 @@
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:G31"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="I6:M6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A7:A16"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:F19"/>
-    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="A135:B135"/>
+    <mergeCell ref="A136:B136"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="D83:E83"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="D84:E84"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="F86:G86"/>
     <mergeCell ref="A89:E89"/>
     <mergeCell ref="A90:E90"/>
     <mergeCell ref="A91:E91"/>
     <mergeCell ref="B92:D92"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="B98:D98"/>
-    <mergeCell ref="B99:D99"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="F99:G99"/>
-    <mergeCell ref="B131:D131"/>
-    <mergeCell ref="F131:G131"/>
-    <mergeCell ref="B132:D132"/>
-    <mergeCell ref="F132:G132"/>
-    <mergeCell ref="A101:E101"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="F102:G102"/>
-    <mergeCell ref="B103:D103"/>
-    <mergeCell ref="F103:G103"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="F104:G104"/>
-    <mergeCell ref="B105:D105"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="A122:E122"/>
-    <mergeCell ref="A123:E123"/>
-    <mergeCell ref="A124:E124"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="F126:G126"/>
-    <mergeCell ref="B127:D127"/>
-    <mergeCell ref="F127:G127"/>
-    <mergeCell ref="B128:D128"/>
-    <mergeCell ref="F128:G128"/>
-    <mergeCell ref="B129:D129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="B130:D130"/>
-    <mergeCell ref="F130:G130"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="F106:G106"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="F107:G107"/>
-    <mergeCell ref="B108:D108"/>
-    <mergeCell ref="F108:G108"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="F109:G109"/>
-    <mergeCell ref="A125:E125"/>
-    <mergeCell ref="B133:D133"/>
-    <mergeCell ref="F133:G133"/>
-    <mergeCell ref="B134:D134"/>
-    <mergeCell ref="F134:G134"/>
-    <mergeCell ref="B135:D135"/>
-    <mergeCell ref="F135:G135"/>
-    <mergeCell ref="B136:D136"/>
-    <mergeCell ref="F136:G136"/>
-    <mergeCell ref="B137:D137"/>
-    <mergeCell ref="F137:G137"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="F141:G141"/>
-    <mergeCell ref="F142:G142"/>
-    <mergeCell ref="A162:E162"/>
-    <mergeCell ref="C177:D177"/>
-    <mergeCell ref="C178:D178"/>
-    <mergeCell ref="C179:D179"/>
-    <mergeCell ref="E177:F177"/>
-    <mergeCell ref="E178:F178"/>
-    <mergeCell ref="E179:F179"/>
-    <mergeCell ref="A179:B179"/>
-    <mergeCell ref="A163:C163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="A167:E167"/>
-    <mergeCell ref="B168:C168"/>
-    <mergeCell ref="F172:G172"/>
-    <mergeCell ref="B169:C169"/>
-    <mergeCell ref="B170:C170"/>
-    <mergeCell ref="B171:C171"/>
-    <mergeCell ref="B172:C172"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="A164:C164"/>
-    <mergeCell ref="A175:E175"/>
-    <mergeCell ref="A176:B176"/>
-    <mergeCell ref="A182:E182"/>
-    <mergeCell ref="A183:D183"/>
-    <mergeCell ref="E183:G183"/>
-    <mergeCell ref="A201:E201"/>
-    <mergeCell ref="B202:C202"/>
-    <mergeCell ref="D202:E202"/>
-    <mergeCell ref="D203:E203"/>
-    <mergeCell ref="A184:D184"/>
-    <mergeCell ref="E184:G184"/>
-    <mergeCell ref="B203:C203"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
